--- a/workbooks/08 Formulas 4 - Lookups.xlsx
+++ b/workbooks/08 Formulas 4 - Lookups.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="725">
   <si>
     <t>Challenge</t>
   </si>
@@ -2221,22 +2221,94 @@
     <t>Boss F5</t>
   </si>
   <si>
+    <t>Shift+8.</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>ASTERISK</t>
+  </si>
+  <si>
     <t>F5</t>
   </si>
   <si>
     <t>Boss F6</t>
   </si>
   <si>
+    <t>SUM plus IF.</t>
+  </si>
+  <si>
+    <t>=SUMIF</t>
+  </si>
+  <si>
+    <t>=SUMIF(</t>
+  </si>
+  <si>
+    <t>=SUMIF()</t>
+  </si>
+  <si>
+    <t>SUMIF</t>
+  </si>
+  <si>
+    <t>SUMIF(</t>
+  </si>
+  <si>
+    <t>SUMIF()</t>
+  </si>
+  <si>
     <t>F6</t>
   </si>
   <si>
     <t>Boss F7</t>
   </si>
   <si>
+    <t>AVERAGE plus IF.</t>
+  </si>
+  <si>
+    <t>=AVERAGEIF</t>
+  </si>
+  <si>
+    <t>=AVERAGEIF(</t>
+  </si>
+  <si>
+    <t>=AVERAGEIF()</t>
+  </si>
+  <si>
+    <t>AVERAGEIF</t>
+  </si>
+  <si>
+    <t>AVERAGEIF(</t>
+  </si>
+  <si>
+    <t>AVERAGEIF()</t>
+  </si>
+  <si>
     <t>F7</t>
   </si>
   <si>
     <t>Boss F8</t>
+  </si>
+  <si>
+    <t>COUNTIF plus S.</t>
+  </si>
+  <si>
+    <t>=COUNTIFS</t>
+  </si>
+  <si>
+    <t>=COUNTIFS(</t>
+  </si>
+  <si>
+    <t>=COUNTIFS()</t>
+  </si>
+  <si>
+    <t>COUNTIFS</t>
+  </si>
+  <si>
+    <t>COUNTIFS(</t>
+  </si>
+  <si>
+    <t>COUNTIFS()</t>
   </si>
   <si>
     <t>F8</t>
@@ -3239,7 +3311,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>635</v>
+        <v>659</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3249,12 +3321,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>636</v>
+        <v>660</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>637</v>
+        <v>661</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3264,32 +3336,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>638</v>
+        <v>662</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>639</v>
+        <v>663</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>640</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>641</v>
+        <v>665</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>642</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>643</v>
+        <v>667</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3299,30 +3371,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>644</v>
+        <v>668</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>645</v>
+        <v>669</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>493</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>646</v>
+        <v>670</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>647</v>
+        <v>671</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>648</v>
+        <v>672</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>649</v>
+        <v>673</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>650</v>
+        <v>674</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F4-1 Seeker'!$G$12:$G$34)&amp;" / 160"</f>
@@ -3337,15 +3409,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>651</v>
+        <v>675</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>652</v>
+        <v>676</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>653</v>
+        <v>677</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F4-2 Safety Net'!$G$12:$G$34)&amp;" / 160"</f>
@@ -3360,15 +3432,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>654</v>
+        <v>678</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>655</v>
+        <v>679</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>656</v>
+        <v>680</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F4-3 Old School'!$G$12:$G$34)&amp;" / 160"</f>
@@ -3383,15 +3455,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>657</v>
+        <v>681</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>658</v>
+        <v>682</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>659</v>
+        <v>683</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM('F4-4 Power Couple'!$G$14:$G$42)&amp;" / 220"</f>
@@ -3406,15 +3478,15 @@
         <v>NEW</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>660</v>
+        <v>684</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>661</v>
+        <v>685</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>662</v>
+        <v>686</v>
       </c>
       <c r="C17" s="9" cm="1" t="str">
         <f t="array" ref="C17">SUM('F4-5 Tiers'!$G$12:$G$34)&amp;" / 160"</f>
@@ -3429,15 +3501,15 @@
         <v>NEW</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>663</v>
+        <v>687</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="7" t="s">
-        <v>664</v>
+        <v>688</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>665</v>
+        <v>689</v>
       </c>
       <c r="C18" s="9" cm="1" t="str">
         <f t="array" ref="C18">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3452,12 +3524,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>666</v>
+        <v>690</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>667</v>
+        <v>691</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">(SUM('F4-1 Seeker'!$G$12:$G$34)+SUM('F4-2 Safety Net'!$G$12:$G$34)+SUM('F4-3 Old School'!$G$12:$G$34)+SUM('F4-4 Power Couple'!$G$14:$G$42)+SUM('F4-5 Tiers'!$G$12:$G$34)+SUM(Boss!$G$14:$G$33))&amp;" / 1020"</f>
@@ -3466,19 +3538,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>668</v>
+        <v>692</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">_xlfn.LET(_xlpm.p,(SUM('F4-1 Seeker'!$G$12:$G$34)+SUM('F4-2 Safety Net'!$G$12:$G$34)+SUM('F4-3 Old School'!$G$12:$G$34)+SUM('F4-4 Power Couple'!$G$14:$G$42)+SUM('F4-5 Tiers'!$G$12:$G$34)+SUM(Boss!$G$14:$G$33))/1020,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=15),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>669</v>
+        <v>693</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>670</v>
+        <v>694</v>
       </c>
       <c r="B22" s="12" cm="1" t="str">
         <f t="array" ref="B22">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 15)","—")</f>
@@ -3487,7 +3559,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="7" t="s">
-        <v>671</v>
+        <v>695</v>
       </c>
       <c r="B23" s="12" cm="1" t="str">
         <f t="array" ref="B23">IFERROR(INDEX($A$13:$A$17,MATCH("☆☆☆",$D$13:$D$17,0))&amp;" "&amp;INDEX($B$13:$B$17,MATCH("☆☆☆",$D$13:$D$17,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
@@ -3496,7 +3568,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="13" t="s">
-        <v>672</v>
+        <v>696</v>
       </c>
     </row>
   </sheetData>
@@ -4586,7 +4658,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>633</v>
+        <v>657</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4597,7 +4669,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>634</v>
+        <v>658</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -4793,17 +4865,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="51.25" customHeight="1">
+    <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B18" s="33" cm="1" t="str">
-        <f t="array" ref="B18">IF($C$10="OPEN","Which classic function searches the first column of a table and returns a column by number?  (from F4-3 Old School)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
+        <f t="array" ref="B18">IF($C$10="OPEN","Which wildcard matches any number of characters?  (from F3-1 Counters)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
-        <f t="array" ref="D18">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$18,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$92:$J$92),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
+        <f t="array" ref="D18">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$18,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$92:$F$92),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E18" s="22"/>
@@ -4818,15 +4890,15 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>594</v>
+        <v>604</v>
       </c>
       <c r="B19" s="33" cm="1" t="str">
-        <f t="array" ref="B19">IF($C$10="OPEN","Which 4th argument makes VLOOKUP find an exact match?  (from F4-3 Old School)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
+        <f t="array" ref="B19">IF($C$10="OPEN","Which function adds values that meet one condition?  (from F3-2 Money Bags)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
-        <f t="array" ref="D19">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$19,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$93:$F$93),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
+        <f t="array" ref="D19">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$19,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$93:$J$93),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E19" s="22"/>
@@ -4841,10 +4913,10 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="B20" s="33" cm="1" t="str">
-        <f t="array" ref="B20">IF($C$10="OPEN","Which function returns the item at a given position in a range?  (from F4-4 Power Couple)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
+        <f t="array" ref="B20">IF($C$10="OPEN","Which function averages values that meet one condition?  (from F3-2 Money Bags)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C20" s="20"/>
@@ -4864,10 +4936,10 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="B21" s="33" cm="1" t="str">
-        <f t="array" ref="B21">IF($C$10="OPEN","Which function returns the position of a value in a range?  (from F4-4 Power Couple)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
+        <f t="array" ref="B21">IF($C$10="OPEN","Which function counts rows that meet several conditions?  (from F3-3 Multi-Filter)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C21" s="20"/>
@@ -4887,7 +4959,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>599</v>
+        <v>623</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -4898,7 +4970,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>600</v>
+        <v>624</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4926,14 +4998,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>603</v>
+        <v>627</v>
       </c>
       <c r="B26" s="33" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In J6 return the Price of the ID in I6 with XLOOKUP.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>604</v>
+        <v>628</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$6),ABS('Boss Arena'!$J$6-Key!$C$96)&lt;=1E-9*MAX(1,ABS(Key!$C$96))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use XLOOKUP"))))),"LOCKED")</f>
@@ -4951,14 +5023,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="B27" s="33" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In J9 return the Stock of I9 with locked ranges, then fill down to J12.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>608</v>
+        <v>632</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$J$9,'Boss Arena'!$J$10,'Boss Arena'!$J$11,'Boss Arena'!$J$12)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$12))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$J$9),ISERROR('Boss Arena'!$J$10),ISERROR('Boss Arena'!$J$11),ISERROR('Boss Arena'!$J$12)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$9),ABS('Boss Arena'!$J$9-Key!$E$97)&lt;=1E-9*MAX(1,ABS(Key!$E$97))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$J$10),ABS('Boss Arena'!$J$10-Key!$F$97)&lt;=1E-9*MAX(1,ABS(Key!$F$97))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$J$11),ABS('Boss Arena'!$J$11-Key!$G$97)&lt;=1E-9*MAX(1,ABS(Key!$G$97))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$J$12),ABS('Boss Arena'!$J$12-Key!$H$97)&lt;=1E-9*MAX(1,ABS(Key!$H$97))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$9)))))),IF(ISNUMBER(FIND("$",_xlfn.FORMULATEXT('Boss Arena'!$J$9))),"✔ CLEAR","✘ CLOSE · add $ so it fills correctly (F4)"),"✘ CLOSE · right value, but use XLOOKUP"))))),"LOCKED")</f>
@@ -4976,14 +5048,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>611</v>
+        <v>635</v>
       </c>
       <c r="B28" s="33" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In J15 look up the Product for I15 and show ""Not found"" when it is missing.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>612</v>
+        <v>636</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$15),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$15)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$15),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$15),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$J$15),'Boss Arena'!$J$15=Key!$C$98),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$15)))))),"✔ CLEAR","✘ CLOSE · right value, but use XLOOKUP"))))),"LOCKED")</f>
@@ -5001,14 +5073,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="B29" s="33" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In J18 return the Price AND the Stock of I18 with one XLOOKUP.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>616</v>
+        <v>640</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$18),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$18)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$18),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$18),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$J$18))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2101)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$J$18))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2101)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$J$18)=_xlfn.ANCHORARRAY(Key!$E$2101)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2101))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2101))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$18)))))),"✔ CLEAR","✘ CLOSE · right result, but use XLOOKUP"),"✘ TRY AGAIN")))),"LOCKED")</f>
@@ -5026,14 +5098,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>619</v>
+        <v>643</v>
       </c>
       <c r="B30" s="33" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In J21 return the Category of I21 with VLOOKUP (exact match).","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>620</v>
+        <v>644</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$21),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$21)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$21),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$21),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$J$21),'Boss Arena'!$J$21=Key!$C$100),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"VLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$21)))))),"✔ CLEAR","✘ CLOSE · right value, but use VLOOKUP"))))),"LOCKED")</f>
@@ -5051,14 +5123,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>623</v>
+        <v>647</v>
       </c>
       <c r="B31" s="33" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In J24 return the ID of the product named in I24 (the ID is to the LEFT). Use INDEX and MATCH.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>624</v>
+        <v>648</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$24),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$24)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$24),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$24),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$J$24),'Boss Arena'!$J$24=Key!$C$101),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"INDEX"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$24))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MATCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$24)))))),"✔ CLEAR","✘ CLOSE · right value, but use INDEX and MATCH"))))),"LOCKED")</f>
@@ -5076,14 +5148,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>627</v>
+        <v>651</v>
       </c>
       <c r="B32" s="33" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In J27 return the position of I27 in C6:C20 with XMATCH.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>628</v>
+        <v>652</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$27),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$27)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$27),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$27),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$27),ABS('Boss Arena'!$J$27-Key!$C$102)&lt;=1E-9*MAX(1,ABS(Key!$C$102))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XMATCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$27)))))),"✔ CLEAR","✘ CLOSE · right value, but use XMATCH"))))),"LOCKED")</f>
@@ -5101,14 +5173,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>631</v>
+        <v>655</v>
       </c>
       <c r="B33" s="33" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","In J30 find the discount tier for the quantity in I30 from L6:M9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>632</v>
+        <v>656</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$30),ABS('Boss Arena'!$J$30-Key!$C$103)&lt;=1E-9*MAX(1,ABS(Key!$C$103))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$30)))))),IF(ISNUMBER(FIND("-1",_xlfn.FORMULATEXT('Boss Arena'!$J$30))),"✔ CLEAR","✘ CLOSE · your formula needs -1"),"✘ CLOSE · right value, but use XLOOKUP"))))),"LOCKED")</f>
@@ -5681,7 +5753,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>673</v>
+        <v>697</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5689,189 +5761,189 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>674</v>
+        <v>698</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>644</v>
+        <v>668</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>675</v>
+        <v>699</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>676</v>
+        <v>700</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="51.25" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>649</v>
+        <v>673</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>54</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>677</v>
+        <v>701</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>678</v>
+        <v>702</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>649</v>
+        <v>673</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>57</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>679</v>
+        <v>703</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>680</v>
+        <v>704</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>652</v>
+        <v>676</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>142</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>681</v>
+        <v>705</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>682</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="35.5" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>652</v>
+        <v>676</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>178</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>683</v>
+        <v>707</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>684</v>
+        <v>708</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="35.5" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>655</v>
+        <v>679</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>685</v>
+        <v>709</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>686</v>
+        <v>710</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>655</v>
+        <v>679</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>141</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>687</v>
+        <v>711</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>688</v>
+        <v>712</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="35.5" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>658</v>
+        <v>682</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>134</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>689</v>
+        <v>713</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>690</v>
+        <v>714</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="35.5" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>658</v>
+        <v>682</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>135</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>691</v>
+        <v>715</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>692</v>
+        <v>716</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="35.5" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>658</v>
+        <v>682</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>237</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>693</v>
+        <v>717</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="19.75" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>658</v>
+        <v>682</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>339</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>695</v>
+        <v>719</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>696</v>
+        <v>720</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>661</v>
+        <v>685</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>241</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>697</v>
+        <v>721</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>698</v>
+        <v>722</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>661</v>
+        <v>685</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>143</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>699</v>
+        <v>723</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>700</v>
+        <v>724</v>
       </c>
     </row>
   </sheetData>
@@ -7656,99 +7728,99 @@
         <v>591</v>
       </c>
       <c r="B92" t="s">
-        <v>338</v>
+        <v>592</v>
       </c>
       <c r="E92" t="s">
-        <v>346</v>
+        <v>593</v>
       </c>
       <c r="F92" t="s">
-        <v>347</v>
-      </c>
-      <c r="G92" t="s">
-        <v>348</v>
-      </c>
-      <c r="H92" t="s">
-        <v>136</v>
-      </c>
-      <c r="I92" t="s">
-        <v>349</v>
-      </c>
-      <c r="J92" t="s">
-        <v>350</v>
+        <v>594</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B93" t="s">
-        <v>342</v>
+        <v>597</v>
       </c>
       <c r="E93" t="s">
-        <v>352</v>
+        <v>598</v>
       </c>
       <c r="F93" t="s">
-        <v>353</v>
+        <v>599</v>
+      </c>
+      <c r="G93" t="s">
+        <v>600</v>
+      </c>
+      <c r="H93" t="s">
+        <v>601</v>
+      </c>
+      <c r="I93" t="s">
+        <v>602</v>
+      </c>
+      <c r="J93" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="B94" t="s">
-        <v>433</v>
+        <v>606</v>
       </c>
       <c r="E94" t="s">
-        <v>448</v>
+        <v>607</v>
       </c>
       <c r="F94" t="s">
-        <v>449</v>
+        <v>608</v>
       </c>
       <c r="G94" t="s">
-        <v>450</v>
+        <v>609</v>
       </c>
       <c r="H94" t="s">
-        <v>134</v>
+        <v>610</v>
       </c>
       <c r="I94" t="s">
-        <v>451</v>
+        <v>611</v>
       </c>
       <c r="J94" t="s">
-        <v>452</v>
+        <v>612</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>597</v>
+        <v>614</v>
       </c>
       <c r="B95" t="s">
-        <v>436</v>
+        <v>615</v>
       </c>
       <c r="E95" t="s">
-        <v>454</v>
+        <v>616</v>
       </c>
       <c r="F95" t="s">
-        <v>455</v>
+        <v>617</v>
       </c>
       <c r="G95" t="s">
-        <v>456</v>
+        <v>618</v>
       </c>
       <c r="H95" t="s">
-        <v>135</v>
+        <v>619</v>
       </c>
       <c r="I95" t="s">
-        <v>457</v>
+        <v>620</v>
       </c>
       <c r="J95" t="s">
-        <v>458</v>
+        <v>621</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="B96" t="s">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="C96" cm="1">
         <f t="array" ref="C96">_xlfn.XLOOKUP('Boss Arena'!$I$6,'Boss Arena'!$B$6:$B$20,'Boss Arena'!$E$6:$E$20)</f>
@@ -7757,10 +7829,10 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>605</v>
+        <v>629</v>
       </c>
       <c r="B97" t="s">
-        <v>606</v>
+        <v>630</v>
       </c>
       <c r="E97" cm="1">
         <f t="array" ref="E97">_xlfn.XLOOKUP('Boss Arena'!$I$9,'Boss Arena'!$B$6:$B$20,'Boss Arena'!$F$6:$F$20)</f>
@@ -7781,10 +7853,10 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="B98" t="s">
-        <v>610</v>
+        <v>634</v>
       </c>
       <c r="C98" cm="1" t="str">
         <f t="array" ref="C98">_xlfn.XLOOKUP('Boss Arena'!$I$15,'Boss Arena'!$B$6:$B$20,'Boss Arena'!$C$6:$C$20,"Not found")</f>
@@ -7793,18 +7865,18 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>613</v>
+        <v>637</v>
       </c>
       <c r="B99" t="s">
-        <v>614</v>
+        <v>638</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>617</v>
+        <v>641</v>
       </c>
       <c r="B100" t="s">
-        <v>618</v>
+        <v>642</v>
       </c>
       <c r="C100" cm="1" t="str">
         <f t="array" ref="C100">VLOOKUP('Boss Arena'!$I$21,'Boss Arena'!$B$6:$F$20,3,FALSE)</f>
@@ -7813,10 +7885,10 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="B101" t="s">
-        <v>622</v>
+        <v>646</v>
       </c>
       <c r="C101" cm="1" t="str">
         <f t="array" ref="C101">INDEX('Boss Arena'!$B$6:$B$20,MATCH('Boss Arena'!$I$24,'Boss Arena'!$C$6:$C$20,0))</f>
@@ -7825,10 +7897,10 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>625</v>
+        <v>649</v>
       </c>
       <c r="B102" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="C102" cm="1">
         <f t="array" ref="C102">_xlfn.XMATCH('Boss Arena'!$I$27,'Boss Arena'!$C$6:$C$20)</f>
@@ -7837,10 +7909,10 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>629</v>
+        <v>653</v>
       </c>
       <c r="B103" t="s">
-        <v>630</v>
+        <v>654</v>
       </c>
       <c r="C103" cm="1">
         <f t="array" ref="C103">_xlfn.XLOOKUP('Boss Arena'!$I$30,'Boss Arena'!$L$6:$L$9,'Boss Arena'!$M$6:$M$9,,-1)</f>

--- a/workbooks/08 Formulas 4 - Lookups.xlsx
+++ b/workbooks/08 Formulas 4 - Lookups.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="731">
   <si>
     <t>Challenge</t>
   </si>
@@ -560,49 +560,52 @@
     <t>T2</t>
   </si>
   <si>
+    <t>Which move is this? Lock lookup ranges with $ before you fill the formula down.</t>
+  </si>
+  <si>
+    <t>CHALLENGES · recall it, then do it</t>
+  </si>
+  <si>
+    <t>▶ Open F4-1 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F4-1 Seeker C1</t>
+  </si>
+  <si>
+    <t>=XLOOKUP</t>
+  </si>
+  <si>
+    <t>=XLOOKUP(</t>
+  </si>
+  <si>
+    <t>=XLOOKUP()</t>
+  </si>
+  <si>
+    <t>XLOOKUP(</t>
+  </si>
+  <si>
+    <t>XLOOKUP()</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>F4-1 Seeker C2</t>
+  </si>
+  <si>
+    <t>$</t>
+  </si>
+  <si>
+    <t>DOLLAR</t>
+  </si>
+  <si>
+    <t>DOLLARSIGN</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
     <t>Which symbol locks a range so it doesn't shift when you fill down?</t>
-  </si>
-  <si>
-    <t>CHALLENGES · recall it, then do it</t>
-  </si>
-  <si>
-    <t>▶ Open F4-1 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F4-1 Seeker C1</t>
-  </si>
-  <si>
-    <t>=XLOOKUP</t>
-  </si>
-  <si>
-    <t>=XLOOKUP(</t>
-  </si>
-  <si>
-    <t>=XLOOKUP()</t>
-  </si>
-  <si>
-    <t>XLOOKUP(</t>
-  </si>
-  <si>
-    <t>XLOOKUP()</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>F4-1 Seeker C2</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
-    <t>DOLLAR</t>
-  </si>
-  <si>
-    <t>DOLLARSIGN</t>
-  </si>
-  <si>
-    <t>C2</t>
   </si>
   <si>
     <t>F4-1 Seeker C3</t>
@@ -915,31 +918,34 @@
     <t>match_mode -1</t>
   </si>
   <si>
+    <t>Which move is this? Give XLOOKUP a return range two columns wide and both values spill out.</t>
+  </si>
+  <si>
+    <t>▶ Open F4-2 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F4-2 Safety Net C1</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>4TH</t>
+  </si>
+  <si>
+    <t>FOURTH</t>
+  </si>
+  <si>
+    <t>IF_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>F4-2 Safety Net C2</t>
+  </si>
+  <si>
+    <t>TWO</t>
+  </si>
+  <si>
     <t>If the return array is E6:F20, how many columns does the result spill into?</t>
-  </si>
-  <si>
-    <t>▶ Open F4-2 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F4-2 Safety Net C1</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>4TH</t>
-  </si>
-  <si>
-    <t>FOURTH</t>
-  </si>
-  <si>
-    <t>IF_NOT_FOUND</t>
-  </si>
-  <si>
-    <t>F4-2 Safety Net C2</t>
-  </si>
-  <si>
-    <t>TWO</t>
   </si>
   <si>
     <t>F4-2 Safety Net C3</t>
@@ -1282,37 +1288,40 @@
     <t>The opposite of TRUE.</t>
   </si>
   <si>
+    <t>Which move is this? End VLOOKUP with FALSE for an exact match.</t>
+  </si>
+  <si>
+    <t>▶ Open F4-3 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F4-3 Old School C1</t>
+  </si>
+  <si>
+    <t>=VLOOKUP</t>
+  </si>
+  <si>
+    <t>=VLOOKUP(</t>
+  </si>
+  <si>
+    <t>=VLOOKUP()</t>
+  </si>
+  <si>
+    <t>VLOOKUP(</t>
+  </si>
+  <si>
+    <t>VLOOKUP()</t>
+  </si>
+  <si>
+    <t>F4-3 Old School C2</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
     <t>Which 4th argument makes VLOOKUP find an exact match?</t>
-  </si>
-  <si>
-    <t>▶ Open F4-3 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F4-3 Old School C1</t>
-  </si>
-  <si>
-    <t>=VLOOKUP</t>
-  </si>
-  <si>
-    <t>=VLOOKUP(</t>
-  </si>
-  <si>
-    <t>=VLOOKUP()</t>
-  </si>
-  <si>
-    <t>VLOOKUP(</t>
-  </si>
-  <si>
-    <t>VLOOKUP()</t>
-  </si>
-  <si>
-    <t>F4-3 Old School C2</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>FALSE</t>
   </si>
   <si>
     <t>F4-3 Old School C3</t>
@@ -1704,61 +1713,64 @@
     <t>T3</t>
   </si>
   <si>
+    <t>Which move is this? =INDEX(return_range, MATCH(value, lookup_range, 0)) looks up in any direction.</t>
+  </si>
+  <si>
+    <t>F4-4 Power Couple T4</t>
+  </si>
+  <si>
+    <t>X plus MATCH.</t>
+  </si>
+  <si>
+    <t>T4</t>
+  </si>
+  <si>
+    <t>Which modern function returns a position with an exact match by default?</t>
+  </si>
+  <si>
+    <t>▶ Open F4-4 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F4-4 Power Couple C1</t>
+  </si>
+  <si>
+    <t>=INDEX</t>
+  </si>
+  <si>
+    <t>=INDEX(</t>
+  </si>
+  <si>
+    <t>=INDEX()</t>
+  </si>
+  <si>
+    <t>INDEX(</t>
+  </si>
+  <si>
+    <t>INDEX()</t>
+  </si>
+  <si>
+    <t>F4-4 Power Couple C2</t>
+  </si>
+  <si>
+    <t>=MATCH</t>
+  </si>
+  <si>
+    <t>=MATCH(</t>
+  </si>
+  <si>
+    <t>=MATCH()</t>
+  </si>
+  <si>
+    <t>MATCH(</t>
+  </si>
+  <si>
+    <t>MATCH()</t>
+  </si>
+  <si>
+    <t>F4-4 Power Couple C3</t>
+  </si>
+  <si>
     <t>Which function goes inside INDEX to find the row position?</t>
-  </si>
-  <si>
-    <t>F4-4 Power Couple T4</t>
-  </si>
-  <si>
-    <t>X plus MATCH.</t>
-  </si>
-  <si>
-    <t>T4</t>
-  </si>
-  <si>
-    <t>Which modern function returns a position with an exact match by default?</t>
-  </si>
-  <si>
-    <t>▶ Open F4-4 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F4-4 Power Couple C1</t>
-  </si>
-  <si>
-    <t>=INDEX</t>
-  </si>
-  <si>
-    <t>=INDEX(</t>
-  </si>
-  <si>
-    <t>=INDEX()</t>
-  </si>
-  <si>
-    <t>INDEX(</t>
-  </si>
-  <si>
-    <t>INDEX()</t>
-  </si>
-  <si>
-    <t>F4-4 Power Couple C2</t>
-  </si>
-  <si>
-    <t>=MATCH</t>
-  </si>
-  <si>
-    <t>=MATCH(</t>
-  </si>
-  <si>
-    <t>=MATCH()</t>
-  </si>
-  <si>
-    <t>MATCH(</t>
-  </si>
-  <si>
-    <t>MATCH()</t>
-  </si>
-  <si>
-    <t>F4-4 Power Couple C3</t>
   </si>
   <si>
     <t>F4-4 Power Couple C4</t>
@@ -2104,40 +2116,46 @@
     <t>Minus one.</t>
   </si>
   <si>
+    <t>Which move is this? XLOOKUP(…,,-1): exact match or the next smaller item.</t>
+  </si>
+  <si>
+    <t>F4-5 Tiers T2</t>
+  </si>
+  <si>
+    <t>Low to high.</t>
+  </si>
+  <si>
+    <t>Which move is this? Approximate VLOOKUP: the first column must be sorted smallest to largest.</t>
+  </si>
+  <si>
+    <t>▶ Open F4-5 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F4-5 Tiers C1</t>
+  </si>
+  <si>
+    <t>-1</t>
+  </si>
+  <si>
     <t>Which XLOOKUP match_mode returns an exact match or the next smaller item?</t>
   </si>
   <si>
-    <t>F4-5 Tiers T2</t>
-  </si>
-  <si>
-    <t>Low to high.</t>
+    <t>F4-5 Tiers C2</t>
+  </si>
+  <si>
+    <t>A-Z</t>
+  </si>
+  <si>
+    <t>ASCENDING</t>
+  </si>
+  <si>
+    <t>ATOZ</t>
+  </si>
+  <si>
+    <t>SMALLESTTOLARGEST</t>
   </si>
   <si>
     <t>For an approximate VLOOKUP, how must the first column be sorted?</t>
-  </si>
-  <si>
-    <t>▶ Open F4-5 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F4-5 Tiers C1</t>
-  </si>
-  <si>
-    <t>-1</t>
-  </si>
-  <si>
-    <t>F4-5 Tiers C2</t>
-  </si>
-  <si>
-    <t>A-Z</t>
-  </si>
-  <si>
-    <t>ASCENDING</t>
-  </si>
-  <si>
-    <t>ATOZ</t>
-  </si>
-  <si>
-    <t>SMALLESTTOLARGEST</t>
   </si>
   <si>
     <t>F4-5 Tiers C3</t>
@@ -3311,7 +3329,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3321,12 +3339,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3336,32 +3354,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3371,30 +3389,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F4-1 Seeker'!$G$12:$G$34)&amp;" / 160"</f>
@@ -3409,15 +3427,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F4-2 Safety Net'!$G$12:$G$34)&amp;" / 160"</f>
@@ -3432,15 +3450,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F4-3 Old School'!$G$12:$G$34)&amp;" / 160"</f>
@@ -3455,15 +3473,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM('F4-4 Power Couple'!$G$14:$G$42)&amp;" / 220"</f>
@@ -3478,15 +3496,15 @@
         <v>NEW</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="C17" s="9" cm="1" t="str">
         <f t="array" ref="C17">SUM('F4-5 Tiers'!$G$12:$G$34)&amp;" / 160"</f>
@@ -3501,15 +3519,15 @@
         <v>NEW</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="7" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="C18" s="9" cm="1" t="str">
         <f t="array" ref="C18">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3524,12 +3542,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">(SUM('F4-1 Seeker'!$G$12:$G$34)+SUM('F4-2 Safety Net'!$G$12:$G$34)+SUM('F4-3 Old School'!$G$12:$G$34)+SUM('F4-4 Power Couple'!$G$14:$G$42)+SUM('F4-5 Tiers'!$G$12:$G$34)+SUM(Boss!$G$14:$G$33))&amp;" / 1020"</f>
@@ -3538,19 +3556,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">_xlfn.LET(_xlpm.p,(SUM('F4-1 Seeker'!$G$12:$G$34)+SUM('F4-2 Safety Net'!$G$12:$G$34)+SUM('F4-3 Old School'!$G$12:$G$34)+SUM('F4-4 Power Couple'!$G$14:$G$42)+SUM('F4-5 Tiers'!$G$12:$G$34)+SUM(Boss!$G$14:$G$33))/1020,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=15),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="B22" s="12" cm="1" t="str">
         <f t="array" ref="B22">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 15)","—")</f>
@@ -3559,7 +3577,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="7" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="B23" s="12" cm="1" t="str">
         <f t="array" ref="B23">IFERROR(INDEX($A$13:$A$17,MATCH("☆☆☆",$D$13:$D$17,0))&amp;" "&amp;INDEX($B$13:$B$17,MATCH("☆☆☆",$D$13:$D$17,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
@@ -3568,7 +3586,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="13" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
     </row>
   </sheetData>
@@ -3606,7 +3624,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3617,7 +3635,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -3669,10 +3687,10 @@
         <v>52</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="67" customHeight="1">
@@ -3680,7 +3698,7 @@
         <v>55</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>143</v>
@@ -3725,7 +3743,7 @@
         <v>67</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="21" cm="1" t="str">
@@ -3747,7 +3765,7 @@
         <v>72</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -3769,7 +3787,7 @@
         <v>79</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -3791,7 +3809,7 @@
         <v>99</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -3813,7 +3831,7 @@
         <v>104</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -3835,7 +3853,7 @@
         <v>109</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -3857,7 +3875,7 @@
         <v>114</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -3879,7 +3897,7 @@
         <v>119</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -3901,7 +3919,7 @@
         <v>124</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -3923,7 +3941,7 @@
         <v>129</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -3979,7 +3997,7 @@
         <v>137</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="21" cm="1" t="str">
@@ -4001,7 +4019,7 @@
         <v>144</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -4031,7 +4049,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="B29" s="11" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -4062,7 +4080,7 @@
         <v>154</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" cm="1" t="str">
@@ -4084,7 +4102,7 @@
         <v>159</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21" cm="1" t="str">
@@ -4103,13 +4121,13 @@
     </row>
     <row r="33" spans="1:7" ht="51.25" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF(ISBLANK('F4-5 Arena'!$J$6),"",IF(NOT(_xlfn.ISFORMULA('F4-5 Arena'!$J$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F4-5 Arena'!$J$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F4-5 Arena'!$J$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F4-5 Arena'!$J$6),ABS('F4-5 Arena'!$J$6-Key!$C$86)&lt;=1E-9*MAX(1,ABS(Key!$C$86))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-5 Arena'!$J$6)))))),IF(ISNUMBER(FIND("-1",_xlfn.FORMULATEXT('F4-5 Arena'!$J$6))),"✔ CLEAR","✘ CLOSE · your formula needs -1"),"✘ CLOSE · right value, but use XLOOKUP")))))</f>
@@ -4127,13 +4145,13 @@
     </row>
     <row r="34" spans="1:7" ht="35.5" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D34" s="21" cm="1" t="str">
         <f t="array" ref="D34">IF(ISBLANK('F4-5 Arena'!$J$9),"",IF(NOT(_xlfn.ISFORMULA('F4-5 Arena'!$J$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F4-5 Arena'!$J$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F4-5 Arena'!$J$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F4-5 Arena'!$J$9),'F4-5 Arena'!$J$9=Key!$C$87),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"VLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-5 Arena'!$J$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use VLOOKUP")))))</f>
@@ -4253,7 +4271,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -4266,10 +4284,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4289,16 +4307,16 @@
         <v>13</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="M5" s="27" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4368,10 +4386,10 @@
         <v>80</v>
       </c>
       <c r="I8" s="27" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J8" s="27" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="L8" s="5">
         <v>50</v>
@@ -4458,10 +4476,10 @@
         <v>60</v>
       </c>
       <c r="L12" s="27" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="M12" s="27" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -4484,7 +4502,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -4507,7 +4525,7 @@
         <v>60</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -4530,7 +4548,7 @@
         <v>70</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -4553,7 +4571,7 @@
         <v>80</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -4576,7 +4594,7 @@
         <v>90</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -4658,7 +4676,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4669,7 +4687,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -4688,7 +4706,7 @@
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -4699,19 +4717,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="7" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C6" s="31"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="7" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="C7" s="31"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="7" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="C8" s="32" cm="1" t="str">
         <f t="array" ref="C8">IF(OR(C6="",C7=""),"",ROUND(MOD(C7-C6,1)*1440,0))</f>
@@ -4720,7 +4738,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="7" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="C9" s="32">
         <v>15</v>
@@ -4728,7 +4746,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="7" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="C10" s="12" cm="1" t="str">
         <f t="array" ref="C10">IF(AND(SUM('F4-1 Seeker'!$G$12:$G$34)&gt;=160*0.5,SUM('F4-2 Safety Net'!$G$12:$G$34)&gt;=160*0.5,SUM('F4-3 Old School'!$G$12:$G$34)&gt;=160*0.5,SUM('F4-4 Power Couple'!$G$14:$G$42)&gt;=220*0.5,SUM('F4-5 Tiers'!$G$12:$G$34)&gt;=160*0.5),"OPEN","LOCKED")</f>
@@ -4741,7 +4759,7 @@
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -4775,7 +4793,7 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="B14" s="33" cm="1" t="str">
         <f t="array" ref="B14">IF($C$10="OPEN","Which XLOOKUP match_mode returns an exact match or the next smaller item?  (from F4-5 Tiers)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4798,7 +4816,7 @@
     </row>
     <row r="15" spans="1:7" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B15" s="33" cm="1" t="str">
         <f t="array" ref="B15">IF($C$10="OPEN","For an approximate VLOOKUP, how must the first column be sorted?  (from F4-5 Tiers)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4821,7 +4839,7 @@
     </row>
     <row r="16" spans="1:7" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="B16" s="33" cm="1" t="str">
         <f t="array" ref="B16">IF($C$10="OPEN","Which XLOOKUP argument number sets the result when no match is found?  (from F4-2 Safety Net)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4844,7 +4862,7 @@
     </row>
     <row r="17" spans="1:7" ht="51.25" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B17" s="33" cm="1" t="str">
         <f t="array" ref="B17">IF($C$10="OPEN","If the return array is E6:F20, how many columns does the result spill into?  (from F4-2 Safety Net)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4867,7 +4885,7 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B18" s="33" cm="1" t="str">
         <f t="array" ref="B18">IF($C$10="OPEN","Which wildcard matches any number of characters?  (from F3-1 Counters)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4890,7 +4908,7 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="B19" s="33" cm="1" t="str">
         <f t="array" ref="B19">IF($C$10="OPEN","Which function adds values that meet one condition?  (from F3-2 Money Bags)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4913,7 +4931,7 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="B20" s="33" cm="1" t="str">
         <f t="array" ref="B20">IF($C$10="OPEN","Which function averages values that meet one condition?  (from F3-2 Money Bags)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4936,7 +4954,7 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="B21" s="33" cm="1" t="str">
         <f t="array" ref="B21">IF($C$10="OPEN","Which function counts rows that meet several conditions?  (from F3-3 Multi-Filter)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4959,7 +4977,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -4970,7 +4988,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4998,14 +5016,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="B26" s="33" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In J6 return the Price of the ID in I6 with XLOOKUP.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$6),ABS('Boss Arena'!$J$6-Key!$C$96)&lt;=1E-9*MAX(1,ABS(Key!$C$96))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use XLOOKUP"))))),"LOCKED")</f>
@@ -5023,14 +5041,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B27" s="33" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In J9 return the Stock of I9 with locked ranges, then fill down to J12.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$J$9,'Boss Arena'!$J$10,'Boss Arena'!$J$11,'Boss Arena'!$J$12)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$12))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$J$9),ISERROR('Boss Arena'!$J$10),ISERROR('Boss Arena'!$J$11),ISERROR('Boss Arena'!$J$12)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$9),ABS('Boss Arena'!$J$9-Key!$E$97)&lt;=1E-9*MAX(1,ABS(Key!$E$97))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$J$10),ABS('Boss Arena'!$J$10-Key!$F$97)&lt;=1E-9*MAX(1,ABS(Key!$F$97))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$J$11),ABS('Boss Arena'!$J$11-Key!$G$97)&lt;=1E-9*MAX(1,ABS(Key!$G$97))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$J$12),ABS('Boss Arena'!$J$12-Key!$H$97)&lt;=1E-9*MAX(1,ABS(Key!$H$97))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$9)))))),IF(ISNUMBER(FIND("$",_xlfn.FORMULATEXT('Boss Arena'!$J$9))),"✔ CLEAR","✘ CLOSE · add $ so it fills correctly (F4)"),"✘ CLOSE · right value, but use XLOOKUP"))))),"LOCKED")</f>
@@ -5048,14 +5066,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="B28" s="33" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In J15 look up the Product for I15 and show ""Not found"" when it is missing.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$15),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$15)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$15),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$15),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$J$15),'Boss Arena'!$J$15=Key!$C$98),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$15)))))),"✔ CLEAR","✘ CLOSE · right value, but use XLOOKUP"))))),"LOCKED")</f>
@@ -5073,14 +5091,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="B29" s="33" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In J18 return the Price AND the Stock of I18 with one XLOOKUP.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$18),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$18)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$18),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$18),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$J$18))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2101)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$J$18))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2101)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$J$18)=_xlfn.ANCHORARRAY(Key!$E$2101)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2101))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2101))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$18)))))),"✔ CLEAR","✘ CLOSE · right result, but use XLOOKUP"),"✘ TRY AGAIN")))),"LOCKED")</f>
@@ -5098,14 +5116,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="B30" s="33" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In J21 return the Category of I21 with VLOOKUP (exact match).","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$21),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$21)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$21),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$21),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$J$21),'Boss Arena'!$J$21=Key!$C$100),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"VLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$21)))))),"✔ CLEAR","✘ CLOSE · right value, but use VLOOKUP"))))),"LOCKED")</f>
@@ -5123,14 +5141,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B31" s="33" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In J24 return the ID of the product named in I24 (the ID is to the LEFT). Use INDEX and MATCH.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$24),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$24)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$24),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$24),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$J$24),'Boss Arena'!$J$24=Key!$C$101),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"INDEX"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$24))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MATCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$24)))))),"✔ CLEAR","✘ CLOSE · right value, but use INDEX and MATCH"))))),"LOCKED")</f>
@@ -5148,14 +5166,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="B32" s="33" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In J27 return the position of I27 in C6:C20 with XMATCH.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$27),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$27)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$27),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$27),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$27),ABS('Boss Arena'!$J$27-Key!$C$102)&lt;=1E-9*MAX(1,ABS(Key!$C$102))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XMATCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$27)))))),"✔ CLEAR","✘ CLOSE · right value, but use XMATCH"))))),"LOCKED")</f>
@@ -5173,14 +5191,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="B33" s="33" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","In J30 find the discount tier for the quantity in I30 from L6:M9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$30),ABS('Boss Arena'!$J$30-Key!$C$103)&lt;=1E-9*MAX(1,ABS(Key!$C$103))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$30)))))),IF(ISNUMBER(FIND("-1",_xlfn.FORMULATEXT('Boss Arena'!$J$30))),"✔ CLEAR","✘ CLOSE · your formula needs -1"),"✘ CLOSE · right value, but use XLOOKUP"))))),"LOCKED")</f>
@@ -5298,7 +5316,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -5311,10 +5329,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -5340,10 +5358,10 @@
         <v>12</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="M5" s="27" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5572,7 +5590,7 @@
         <v>150</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="J15" s="28"/>
     </row>
@@ -5688,7 +5706,7 @@
     </row>
     <row r="23" spans="2:11">
       <c r="I23" s="27" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="J23" s="27" t="s">
         <v>9</v>
@@ -5702,10 +5720,10 @@
     </row>
     <row r="26" spans="2:11">
       <c r="I26" s="27" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="J26" s="27" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="27" spans="2:11">
@@ -5716,10 +5734,10 @@
     </row>
     <row r="29" spans="2:11">
       <c r="I29" s="27" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="30" spans="2:11">
@@ -5753,7 +5771,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5761,189 +5779,189 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="51.25" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>54</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>57</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>142</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="35.5" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="35.5" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>141</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="35.5" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>134</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="35.5" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>135</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="35.5" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="19.75" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>143</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
     </row>
   </sheetData>
@@ -6224,10 +6242,10 @@
     </row>
     <row r="16" spans="1:20">
       <c r="A16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C16" cm="1">
         <f t="array" ref="C16">_xlfn.XLOOKUP('F4-1 Arena'!$I$6,'F4-1 Arena'!$B$6:$B$20,'F4-1 Arena'!$E$6:$E$20)</f>
@@ -6236,10 +6254,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E17" cm="1">
         <f t="array" ref="E17">_xlfn.XLOOKUP('F4-1 Arena'!$I$10,'F4-1 Arena'!$B$6:$B$20,'F4-1 Arena'!$F$6:$F$20)</f>
@@ -6260,7 +6278,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s">
         <v>133</v>
@@ -6286,7 +6304,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s">
         <v>140</v>
@@ -6303,158 +6321,158 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B20" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E21" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G22" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F23" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B24" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E24" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F24" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G24" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H24" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B25" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E25" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F25" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G25" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H25" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B26" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E26" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H26" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B27" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E27" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F27" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G27" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H27" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C28" t="s">
         <v>142</v>
@@ -6466,7 +6484,7 @@
         <v>143</v>
       </c>
       <c r="G28" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H28" t="s">
         <v>141</v>
@@ -6474,67 +6492,67 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B29" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E29" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F29" t="s">
         <v>141</v>
       </c>
       <c r="G29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H29" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B30" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E30" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G30" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H30" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B31" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E31" t="s">
         <v>55</v>
       </c>
       <c r="F31" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B32" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C32" cm="1" t="str">
         <f t="array" ref="C32">_xlfn.XLOOKUP('F4-2 Arena'!$I$6,'F4-2 Arena'!$B$6:$B$20,'F4-2 Arena'!$C$6:$C$20,"Not found")</f>
@@ -6543,248 +6561,248 @@
     </row>
     <row r="33" spans="1:20">
       <c r="A33" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B33" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" spans="1:20">
       <c r="A34" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B34" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E34" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G34" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H34" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="1:20">
       <c r="A35" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E35" t="s">
         <v>55</v>
       </c>
       <c r="F35" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="1:20">
       <c r="A36" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B36" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E36" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F36" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" spans="1:20">
       <c r="A37" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B37" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E37" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:20">
       <c r="A38" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B38" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E38" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F38" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" spans="1:20">
       <c r="A39" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B39" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E39" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F39" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G39" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H39" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I39" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J39" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K39" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L39" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M39" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N39" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O39" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P39" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q39" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="R39" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="S39" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="T39" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:20">
       <c r="A40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E40" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F40" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G40" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H40" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I40" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J40" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K40" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L40" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M40" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N40" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O40" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P40" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q40" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="R40" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="S40" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="T40" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="41" spans="1:20">
       <c r="A41" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E41" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="42" spans="1:20">
       <c r="A42" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B42" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E42" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F42" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G42" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H42" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="43" spans="1:20">
       <c r="A43" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B43" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E43" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F43" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="44" spans="1:20">
       <c r="A44" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C44" t="s">
         <v>136</v>
@@ -6796,7 +6814,7 @@
         <v>135</v>
       </c>
       <c r="G44" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H44" t="s">
         <v>134</v>
@@ -6804,10 +6822,10 @@
     </row>
     <row r="45" spans="1:20">
       <c r="A45" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B45" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C45" t="s">
         <v>141</v>
@@ -6819,7 +6837,7 @@
         <v>143</v>
       </c>
       <c r="G45" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H45" t="s">
         <v>141</v>
@@ -6827,50 +6845,50 @@
     </row>
     <row r="46" spans="1:20">
       <c r="A46" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B46" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E46" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F46" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G46" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H46" t="s">
         <v>136</v>
       </c>
       <c r="I46" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J46" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="47" spans="1:20">
       <c r="A47" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B47" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E47" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F47" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="48" spans="1:20">
       <c r="A48" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B48" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C48" cm="1" t="str">
         <f t="array" ref="C48">VLOOKUP('F4-3 Arena'!$I$6,'F4-3 Arena'!$B$6:$F$20,3,FALSE)</f>
@@ -6879,10 +6897,10 @@
     </row>
     <row r="49" spans="1:20">
       <c r="A49" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B49" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C49" cm="1">
         <f t="array" ref="C49">VLOOKUP('F4-3 Arena'!$I$9,'F4-3 Arena'!$B$6:$F$20,5,FALSE)</f>
@@ -6891,210 +6909,210 @@
     </row>
     <row r="50" spans="1:20">
       <c r="A50" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E50" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F50" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H50" t="s">
         <v>136</v>
       </c>
       <c r="I50" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J50" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="51" spans="1:20">
       <c r="A51" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F51" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="52" spans="1:20">
       <c r="A52" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B52" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E52" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F52" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="53" spans="1:20">
       <c r="A53" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E53" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F53" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="54" spans="1:20">
       <c r="A54" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s">
         <v>65</v>
       </c>
       <c r="E54" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="55" spans="1:20">
       <c r="A55" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E55" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="56" spans="1:20">
       <c r="A56" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B56" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E56" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F56" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G56" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="H56" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="57" spans="1:20">
       <c r="A57" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B57" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E57" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F57" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="G57" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H57" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="58" spans="1:20">
       <c r="A58" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B58" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E58" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F58" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="59" spans="1:20">
       <c r="A59" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B59" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E59" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F59" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G59" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="H59" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="I59" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="J59" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="K59" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="L59" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="M59" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="N59" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="O59" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="P59" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="Q59" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="R59" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="S59" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="T59" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="60" spans="1:20">
       <c r="A60" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B60" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C60" t="s">
         <v>134</v>
@@ -7103,7 +7121,7 @@
         <v>134</v>
       </c>
       <c r="F60" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G60" t="s">
         <v>135</v>
@@ -7114,10 +7132,10 @@
     </row>
     <row r="61" spans="1:20">
       <c r="A61" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B61" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C61" t="s">
         <v>135</v>
@@ -7137,16 +7155,16 @@
     </row>
     <row r="62" spans="1:20">
       <c r="A62" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C62" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E62" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F62" t="s">
         <v>142</v>
@@ -7155,18 +7173,18 @@
         <v>57</v>
       </c>
       <c r="H62" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="63" spans="1:20">
       <c r="A63" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C63" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E63" t="s">
         <v>134</v>
@@ -7175,7 +7193,7 @@
         <v>136</v>
       </c>
       <c r="G63" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H63" t="s">
         <v>54</v>
@@ -7183,62 +7201,62 @@
     </row>
     <row r="64" spans="1:20">
       <c r="A64" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B64" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E64" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F64" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="G64" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="H64" t="s">
         <v>134</v>
       </c>
       <c r="I64" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="J64" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="65" spans="1:20">
       <c r="A65" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B65" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E65" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F65" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="G65" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="H65" t="s">
         <v>135</v>
       </c>
       <c r="I65" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="J65" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="66" spans="1:20">
       <c r="A66" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B66" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E66" t="s">
         <v>135</v>
@@ -7246,36 +7264,36 @@
     </row>
     <row r="67" spans="1:20">
       <c r="A67" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B67" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E67" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F67" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="G67" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="H67" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I67" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="J67" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="68" spans="1:20">
       <c r="A68" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B68" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C68" cm="1">
         <f t="array" ref="C68">MATCH('F4-4 Arena'!$I$6,'F4-4 Arena'!$C$6:$C$20,0)</f>
@@ -7284,10 +7302,10 @@
     </row>
     <row r="69" spans="1:20">
       <c r="A69" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B69" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C69" cm="1" t="str">
         <f t="array" ref="C69">INDEX('F4-4 Arena'!$B$6:$B$20,MATCH('F4-4 Arena'!$I$9,'F4-4 Arena'!$C$6:$C$20,0))</f>
@@ -7296,10 +7314,10 @@
     </row>
     <row r="70" spans="1:20">
       <c r="A70" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B70" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C70" cm="1">
         <f t="array" ref="C70">_xlfn.XMATCH('F4-4 Arena'!$I$12,'F4-4 Arena'!$C$6:$C$20)</f>
@@ -7308,10 +7326,10 @@
     </row>
     <row r="71" spans="1:20">
       <c r="A71" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B71" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C71" cm="1">
         <f t="array" ref="C71">INDEX('F4-4 Arena'!$E$6:$E$20,5)</f>
@@ -7320,62 +7338,62 @@
     </row>
     <row r="72" spans="1:20">
       <c r="A72" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B72" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E72" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F72" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="G72" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="H72" t="s">
         <v>134</v>
       </c>
       <c r="I72" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="J72" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="73" spans="1:20">
       <c r="A73" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B73" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E73" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F73" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="G73" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="H73" t="s">
         <v>135</v>
       </c>
       <c r="I73" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="J73" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="74" spans="1:20">
       <c r="A74" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B74" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E74" t="s">
         <v>135</v>
@@ -7383,33 +7401,33 @@
     </row>
     <row r="75" spans="1:20">
       <c r="A75" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B75" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E75" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F75" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="G75" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="H75" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I75" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="J75" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="76" spans="1:20">
       <c r="A76" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B76" t="s">
         <v>133</v>
@@ -7435,7 +7453,7 @@
     </row>
     <row r="77" spans="1:20">
       <c r="A77" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B77" t="s">
         <v>140</v>
@@ -7452,126 +7470,126 @@
     </row>
     <row r="78" spans="1:20">
       <c r="A78" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B78" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E78" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F78" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="G78" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="H78" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="I78" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="J78" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="K78" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="L78" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="M78" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="N78" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="O78" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="P78" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="Q78" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="R78" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="S78" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="T78" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="79" spans="1:20">
       <c r="A79" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B79" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E79" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="F79" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="80" spans="1:20">
       <c r="A80" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B80" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E80" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F80" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="G80" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="H80" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="I80" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="J80" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B81" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="E81" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B82" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C82" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E82" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F82" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G82" t="s">
         <v>57</v>
@@ -7582,64 +7600,64 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B83" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="C83" t="s">
         <v>143</v>
       </c>
       <c r="E83" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F83" t="s">
         <v>143</v>
       </c>
       <c r="G83" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H83" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B84" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="E84" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B85" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="E85" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="F85" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="G85" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="H85" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B86" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C86" cm="1">
         <f t="array" ref="C86">_xlfn.XLOOKUP('F4-5 Arena'!$I$6,'F4-5 Arena'!$L$6:$L$9,'F4-5 Arena'!$M$6:$M$9,,-1)</f>
@@ -7648,10 +7666,10 @@
     </row>
     <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="B87" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C87" cm="1" t="str">
         <f t="array" ref="C87">VLOOKUP('F4-5 Arena'!$I$9,'F4-5 Arena'!$L$13:$M$17,2,TRUE)</f>
@@ -7660,167 +7678,167 @@
     </row>
     <row r="88" spans="1:10">
       <c r="A88" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B88" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="E88" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B89" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="E89" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="F89" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="G89" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="H89" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="B90" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E90" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F90" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G90" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H90" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B91" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E91" t="s">
         <v>55</v>
       </c>
       <c r="F91" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="B92" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="E92" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F92" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="B93" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="E93" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="F93" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="G93" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="H93" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="I93" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="J93" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B94" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="E94" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="F94" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="G94" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="H94" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="I94" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="J94" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="B95" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="E95" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="F95" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="G95" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="H95" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="I95" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="J95" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="B96" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="C96" cm="1">
         <f t="array" ref="C96">_xlfn.XLOOKUP('Boss Arena'!$I$6,'Boss Arena'!$B$6:$B$20,'Boss Arena'!$E$6:$E$20)</f>
@@ -7829,10 +7847,10 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="B97" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="E97" cm="1">
         <f t="array" ref="E97">_xlfn.XLOOKUP('Boss Arena'!$I$9,'Boss Arena'!$B$6:$B$20,'Boss Arena'!$F$6:$F$20)</f>
@@ -7853,10 +7871,10 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="B98" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="C98" cm="1" t="str">
         <f t="array" ref="C98">_xlfn.XLOOKUP('Boss Arena'!$I$15,'Boss Arena'!$B$6:$B$20,'Boss Arena'!$C$6:$C$20,"Not found")</f>
@@ -7865,18 +7883,18 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="B99" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="B100" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="C100" cm="1" t="str">
         <f t="array" ref="C100">VLOOKUP('Boss Arena'!$I$21,'Boss Arena'!$B$6:$F$20,3,FALSE)</f>
@@ -7885,10 +7903,10 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="B101" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="C101" cm="1" t="str">
         <f t="array" ref="C101">INDEX('Boss Arena'!$B$6:$B$20,MATCH('Boss Arena'!$I$24,'Boss Arena'!$C$6:$C$20,0))</f>
@@ -7897,10 +7915,10 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B102" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C102" cm="1">
         <f t="array" ref="C102">_xlfn.XMATCH('Boss Arena'!$I$27,'Boss Arena'!$C$6:$C$20)</f>
@@ -7909,10 +7927,10 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="B103" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="C103" cm="1">
         <f t="array" ref="C103">_xlfn.XLOOKUP('Boss Arena'!$I$30,'Boss Arena'!$L$6:$L$9,'Boss Arena'!$M$6:$M$9,,-1)</f>
@@ -7956,7 +7974,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7967,7 +7985,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -8434,7 +8452,7 @@
         <v>159</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21" cm="1" t="str">
@@ -8453,13 +8471,13 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF(ISBLANK('F4-1 Arena'!$J$6),"",IF(NOT(_xlfn.ISFORMULA('F4-1 Arena'!$J$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F4-1 Arena'!$J$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F4-1 Arena'!$J$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F4-1 Arena'!$J$6),ABS('F4-1 Arena'!$J$6-Key!$C$16)&lt;=1E-9*MAX(1,ABS(Key!$C$16))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-1 Arena'!$J$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use XLOOKUP")))))</f>
@@ -8477,13 +8495,13 @@
     </row>
     <row r="34" spans="1:7" ht="51.25" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D34" s="21" cm="1" t="str">
         <f t="array" ref="D34">IF(COUNTA('F4-1 Arena'!$J$10,'F4-1 Arena'!$J$11,'F4-1 Arena'!$J$12,'F4-1 Arena'!$J$13)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F4-1 Arena'!$J$10)),NOT(_xlfn.ISFORMULA('F4-1 Arena'!$J$11)),NOT(_xlfn.ISFORMULA('F4-1 Arena'!$J$12)),NOT(_xlfn.ISFORMULA('F4-1 Arena'!$J$13))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F4-1 Arena'!$J$10),ISERROR('F4-1 Arena'!$J$11),ISERROR('F4-1 Arena'!$J$12),ISERROR('F4-1 Arena'!$J$13)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('F4-1 Arena'!$J$10),ABS('F4-1 Arena'!$J$10-Key!$E$17)&lt;=1E-9*MAX(1,ABS(Key!$E$17))),FALSE),IFERROR(AND(ISNUMBER('F4-1 Arena'!$J$11),ABS('F4-1 Arena'!$J$11-Key!$F$17)&lt;=1E-9*MAX(1,ABS(Key!$F$17))),FALSE),IFERROR(AND(ISNUMBER('F4-1 Arena'!$J$12),ABS('F4-1 Arena'!$J$12-Key!$G$17)&lt;=1E-9*MAX(1,ABS(Key!$G$17))),FALSE),IFERROR(AND(ISNUMBER('F4-1 Arena'!$J$13),ABS('F4-1 Arena'!$J$13-Key!$H$17)&lt;=1E-9*MAX(1,ABS(Key!$H$17))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-1 Arena'!$J$10)))))),IF(ISNUMBER(FIND("$",_xlfn.FORMULATEXT('F4-1 Arena'!$J$10))),"✔ CLEAR","✘ CLOSE · add $ so it fills correctly (F4)"),"✘ CLOSE · right value, but use XLOOKUP")))))</f>
@@ -8954,7 +8972,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8965,7 +8983,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -9017,7 +9035,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>142</v>
@@ -9028,10 +9046,10 @@
         <v>55</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="22" customHeight="1">
@@ -9073,7 +9091,7 @@
         <v>67</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="21" cm="1" t="str">
@@ -9095,7 +9113,7 @@
         <v>72</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -9117,7 +9135,7 @@
         <v>79</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -9139,7 +9157,7 @@
         <v>99</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -9161,7 +9179,7 @@
         <v>104</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -9183,7 +9201,7 @@
         <v>109</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -9205,7 +9223,7 @@
         <v>114</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -9227,7 +9245,7 @@
         <v>119</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -9249,7 +9267,7 @@
         <v>124</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -9271,7 +9289,7 @@
         <v>129</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -9327,7 +9345,7 @@
         <v>137</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="21" cm="1" t="str">
@@ -9349,7 +9367,7 @@
         <v>144</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -9379,7 +9397,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="B29" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -9410,7 +9428,7 @@
         <v>154</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" cm="1" t="str">
@@ -9432,7 +9450,7 @@
         <v>159</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21" cm="1" t="str">
@@ -9451,13 +9469,13 @@
     </row>
     <row r="33" spans="1:7" ht="51.25" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF(ISBLANK('F4-2 Arena'!$J$6),"",IF(NOT(_xlfn.ISFORMULA('F4-2 Arena'!$J$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F4-2 Arena'!$J$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F4-2 Arena'!$J$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F4-2 Arena'!$J$6),'F4-2 Arena'!$J$6=Key!$C$32),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-2 Arena'!$J$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use XLOOKUP")))))</f>
@@ -9475,13 +9493,13 @@
     </row>
     <row r="34" spans="1:7" ht="51.25" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D34" s="21" cm="1" t="str">
         <f t="array" ref="D34">IF(ISBLANK('F4-2 Arena'!$J$9),"",IF(NOT(_xlfn.ISFORMULA('F4-2 Arena'!$J$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F4-2 Arena'!$J$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F4-2 Arena'!$J$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F4-2 Arena'!$J$9))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2001)),COLUMNS(_xlfn.ANCHORARRAY('F4-2 Arena'!$J$9))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2001)),SUM(--(_xlfn.ANCHORARRAY('F4-2 Arena'!$J$9)=_xlfn.ANCHORARRAY(Key!$E$2001)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2001))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2001))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-2 Arena'!$J$9)))))),"✔ CLEAR","✘ CLOSE · right result, but use XLOOKUP"),"✘ TRY AGAIN"))))</f>
@@ -9601,7 +9619,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -9614,10 +9632,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -9660,7 +9678,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J6" s="28"/>
     </row>
@@ -9943,7 +9961,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9954,7 +9972,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -10006,7 +10024,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>136</v>
@@ -10017,7 +10035,7 @@
         <v>55</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>141</v>
@@ -10062,7 +10080,7 @@
         <v>67</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="21" cm="1" t="str">
@@ -10084,7 +10102,7 @@
         <v>72</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -10106,7 +10124,7 @@
         <v>79</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -10128,7 +10146,7 @@
         <v>99</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -10150,7 +10168,7 @@
         <v>104</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -10172,7 +10190,7 @@
         <v>109</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -10194,7 +10212,7 @@
         <v>114</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -10216,7 +10234,7 @@
         <v>119</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -10238,7 +10256,7 @@
         <v>124</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -10260,7 +10278,7 @@
         <v>129</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -10316,7 +10334,7 @@
         <v>137</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="21" cm="1" t="str">
@@ -10338,7 +10356,7 @@
         <v>144</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -10368,7 +10386,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="B29" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -10399,7 +10417,7 @@
         <v>154</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" cm="1" t="str">
@@ -10421,7 +10439,7 @@
         <v>159</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21" cm="1" t="str">
@@ -10440,13 +10458,13 @@
     </row>
     <row r="33" spans="1:7" ht="51.25" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF(ISBLANK('F4-3 Arena'!$J$6),"",IF(NOT(_xlfn.ISFORMULA('F4-3 Arena'!$J$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F4-3 Arena'!$J$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F4-3 Arena'!$J$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F4-3 Arena'!$J$6),'F4-3 Arena'!$J$6=Key!$C$48),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"VLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-3 Arena'!$J$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use VLOOKUP")))))</f>
@@ -10464,13 +10482,13 @@
     </row>
     <row r="34" spans="1:7" ht="35.5" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D34" s="21" cm="1" t="str">
         <f t="array" ref="D34">IF(ISBLANK('F4-3 Arena'!$J$9),"",IF(NOT(_xlfn.ISFORMULA('F4-3 Arena'!$J$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F4-3 Arena'!$J$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F4-3 Arena'!$J$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F4-3 Arena'!$J$9),ABS('F4-3 Arena'!$J$9-Key!$C$49)&lt;=1E-9*MAX(1,ABS(Key!$C$49))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"VLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-3 Arena'!$J$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use VLOOKUP")))))</f>
@@ -10590,7 +10608,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -10603,10 +10621,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -10929,7 +10947,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10940,7 +10958,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -10992,7 +11010,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>134</v>
@@ -11003,7 +11021,7 @@
         <v>55</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>135</v>
@@ -11011,24 +11029,24 @@
     </row>
     <row r="9" spans="1:7" ht="67" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
@@ -11070,7 +11088,7 @@
         <v>67</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -11092,7 +11110,7 @@
         <v>72</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -11114,7 +11132,7 @@
         <v>79</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -11136,7 +11154,7 @@
         <v>99</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -11158,7 +11176,7 @@
         <v>104</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -11180,7 +11198,7 @@
         <v>109</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -11202,7 +11220,7 @@
         <v>114</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -11224,7 +11242,7 @@
         <v>119</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -11246,7 +11264,7 @@
         <v>124</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -11268,7 +11286,7 @@
         <v>129</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" cm="1" t="str">
@@ -11324,7 +11342,7 @@
         <v>137</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -11346,7 +11364,7 @@
         <v>144</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -11363,12 +11381,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="35.5" customHeight="1">
+    <row r="29" spans="1:7" ht="51.25" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="21" cm="1" t="str">
@@ -11387,10 +11405,10 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="21" cm="1" t="str">
@@ -11420,7 +11438,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="11" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -11451,7 +11469,7 @@
         <v>154</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -11473,7 +11491,7 @@
         <v>159</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="21" cm="1" t="str">
@@ -11492,10 +11510,10 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>441</v>
+        <v>463</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="21" cm="1" t="str">
@@ -11514,10 +11532,10 @@
     </row>
     <row r="38" spans="1:7" ht="35.5" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -11536,13 +11554,13 @@
     </row>
     <row r="39" spans="1:7" ht="35.5" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(ISBLANK('F4-4 Arena'!$J$6),"",IF(NOT(_xlfn.ISFORMULA('F4-4 Arena'!$J$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F4-4 Arena'!$J$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F4-4 Arena'!$J$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F4-4 Arena'!$J$6),ABS('F4-4 Arena'!$J$6-Key!$C$68)&lt;=1E-9*MAX(1,ABS(Key!$C$68))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MATCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-4 Arena'!$J$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use MATCH")))))</f>
@@ -11560,13 +11578,13 @@
     </row>
     <row r="40" spans="1:7" ht="51.25" customHeight="1">
       <c r="A40" s="18" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="D40" s="21" cm="1" t="str">
         <f t="array" ref="D40">IF(ISBLANK('F4-4 Arena'!$J$9),"",IF(NOT(_xlfn.ISFORMULA('F4-4 Arena'!$J$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F4-4 Arena'!$J$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F4-4 Arena'!$J$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F4-4 Arena'!$J$9),'F4-4 Arena'!$J$9=Key!$C$69),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"INDEX"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-4 Arena'!$J$9))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MATCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-4 Arena'!$J$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use INDEX and MATCH")))))</f>
@@ -11584,13 +11602,13 @@
     </row>
     <row r="41" spans="1:7" ht="35.5" customHeight="1">
       <c r="A41" s="18" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D41" s="21" cm="1" t="str">
         <f t="array" ref="D41">IF(ISBLANK('F4-4 Arena'!$J$12),"",IF(NOT(_xlfn.ISFORMULA('F4-4 Arena'!$J$12)),"✘ That's a typed value · enter a formula",IF(ISERROR('F4-4 Arena'!$J$12),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F4-4 Arena'!$J$12),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F4-4 Arena'!$J$12),ABS('F4-4 Arena'!$J$12-Key!$C$70)&lt;=1E-9*MAX(1,ABS(Key!$C$70))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XMATCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-4 Arena'!$J$12)))))),"✔ CLEAR","✘ CLOSE · right value, but use XMATCH")))))</f>
@@ -11608,13 +11626,13 @@
     </row>
     <row r="42" spans="1:7" ht="35.5" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D42" s="21" cm="1" t="str">
         <f t="array" ref="D42">IF(ISBLANK('F4-4 Arena'!$J$14),"",IF(NOT(_xlfn.ISFORMULA('F4-4 Arena'!$J$14)),"✘ That's a typed value · enter a formula",IF(ISERROR('F4-4 Arena'!$J$14),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F4-4 Arena'!$J$14),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F4-4 Arena'!$J$14),ABS('F4-4 Arena'!$J$14-Key!$C$71)&lt;=1E-9*MAX(1,ABS(Key!$C$71))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"INDEX"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-4 Arena'!$J$14)))))),"✔ CLEAR","✘ CLOSE · right value, but use INDEX")))))</f>
@@ -11762,7 +11780,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -11775,10 +11793,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -11798,10 +11816,10 @@
         <v>13</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -11859,7 +11877,7 @@
         <v>80</v>
       </c>
       <c r="I8" s="27" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="J8" s="27" t="s">
         <v>9</v>
@@ -11920,10 +11938,10 @@
         <v>25</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -11981,7 +11999,7 @@
         <v>40</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J14" s="28"/>
     </row>

--- a/workbooks/08 Formulas 4 - Lookups.xlsx
+++ b/workbooks/08 Formulas 4 - Lookups.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="736">
   <si>
     <t>Challenge</t>
   </si>
@@ -1318,7 +1318,22 @@
     <t>0</t>
   </si>
   <si>
+    <t>=FALSE</t>
+  </si>
+  <si>
+    <t>=FALSE(</t>
+  </si>
+  <si>
+    <t>=FALSE()</t>
+  </si>
+  <si>
     <t>FALSE</t>
+  </si>
+  <si>
+    <t>FALSE(</t>
+  </si>
+  <si>
+    <t>FALSE()</t>
   </si>
   <si>
     <t>Which 4th argument makes VLOOKUP find an exact match?</t>
@@ -1770,25 +1785,25 @@
     <t>F4-4 Power Couple C3</t>
   </si>
   <si>
+    <t>=XMATCH</t>
+  </si>
+  <si>
+    <t>=XMATCH(</t>
+  </si>
+  <si>
+    <t>=XMATCH()</t>
+  </si>
+  <si>
+    <t>XMATCH(</t>
+  </si>
+  <si>
+    <t>XMATCH()</t>
+  </si>
+  <si>
     <t>Which function goes inside INDEX to find the row position?</t>
   </si>
   <si>
     <t>F4-4 Power Couple C4</t>
-  </si>
-  <si>
-    <t>=XMATCH</t>
-  </si>
-  <si>
-    <t>=XMATCH(</t>
-  </si>
-  <si>
-    <t>=XMATCH()</t>
-  </si>
-  <si>
-    <t>XMATCH(</t>
-  </si>
-  <si>
-    <t>XMATCH()</t>
   </si>
   <si>
     <t>F4-4 Power Couple C5</t>
@@ -2551,7 +2566,7 @@
     <t>NEXT UP</t>
   </si>
   <si>
-    <t>Replay a stage: select its yellow answer cells and press Delete. Undo an arena drill with Ctrl+Z.</t>
+    <t>Replay a stage: select a run of its yellow cells (Ctrl+click to add more), then press Delete. Undo an arena drill with Ctrl+Z.</t>
   </si>
   <si>
     <t>CHEAT CODES ▸ LOOKUPS</t>
@@ -3329,7 +3344,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3339,12 +3354,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3354,32 +3369,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3389,30 +3404,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F4-1 Seeker'!$G$12:$G$34)&amp;" / 160"</f>
@@ -3427,15 +3442,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F4-2 Safety Net'!$G$12:$G$34)&amp;" / 160"</f>
@@ -3450,15 +3465,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F4-3 Old School'!$G$12:$G$34)&amp;" / 160"</f>
@@ -3473,15 +3488,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM('F4-4 Power Couple'!$G$14:$G$42)&amp;" / 220"</f>
@@ -3496,15 +3511,15 @@
         <v>NEW</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="C17" s="9" cm="1" t="str">
         <f t="array" ref="C17">SUM('F4-5 Tiers'!$G$12:$G$34)&amp;" / 160"</f>
@@ -3519,15 +3534,15 @@
         <v>NEW</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="7" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="C18" s="9" cm="1" t="str">
         <f t="array" ref="C18">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3542,12 +3557,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">(SUM('F4-1 Seeker'!$G$12:$G$34)+SUM('F4-2 Safety Net'!$G$12:$G$34)+SUM('F4-3 Old School'!$G$12:$G$34)+SUM('F4-4 Power Couple'!$G$14:$G$42)+SUM('F4-5 Tiers'!$G$12:$G$34)+SUM(Boss!$G$14:$G$33))&amp;" / 1020"</f>
@@ -3556,19 +3571,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">_xlfn.LET(_xlpm.p,(SUM('F4-1 Seeker'!$G$12:$G$34)+SUM('F4-2 Safety Net'!$G$12:$G$34)+SUM('F4-3 Old School'!$G$12:$G$34)+SUM('F4-4 Power Couple'!$G$14:$G$42)+SUM('F4-5 Tiers'!$G$12:$G$34)+SUM(Boss!$G$14:$G$33))/1020,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=15),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="B22" s="12" cm="1" t="str">
         <f t="array" ref="B22">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 15)","—")</f>
@@ -3577,16 +3592,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="7" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="B23" s="12" cm="1" t="str">
-        <f t="array" ref="B23">IFERROR(INDEX($A$13:$A$17,MATCH("☆☆☆",$D$13:$D$17,0))&amp;" "&amp;INDEX($B$13:$B$17,MATCH("☆☆☆",$D$13:$D$17,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
+        <f t="array" ref="B23">IFERROR(INDEX($A$13:$A$17,MATCH("☆☆☆",$D$13:$D$17,0))&amp;" "&amp;INDEX($B$13:$B$17,MATCH("☆☆☆",$D$13:$D$17,0)),IF(Start!$E$18="DEFEATED","All clear! Aim for rank S","the Boss"))</f>
         <v>F4-1 Seeker</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="13" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>
@@ -3624,7 +3639,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3635,7 +3650,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -3687,7 +3702,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>242</v>
@@ -3698,7 +3713,7 @@
         <v>55</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>143</v>
@@ -3743,7 +3758,7 @@
         <v>67</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="21" cm="1" t="str">
@@ -3765,7 +3780,7 @@
         <v>72</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -3787,11 +3802,11 @@
         <v>79</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
-        <f t="array" ref="D14">IFERROR(_xlfn.LET(_xlpm.a,'F4-5 Tiers'!$C$14,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$74:$E$74),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D14">IFERROR(_xlfn.LET(_xlpm.a,'F4-5 Tiers'!$C$14,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$74:$P$74),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E14" s="22"/>
@@ -3809,7 +3824,7 @@
         <v>99</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -3875,7 +3890,7 @@
         <v>114</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -3897,7 +3912,7 @@
         <v>119</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -3919,7 +3934,7 @@
         <v>124</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -3941,7 +3956,7 @@
         <v>129</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -3997,7 +4012,7 @@
         <v>137</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="21" cm="1" t="str">
@@ -4019,7 +4034,7 @@
         <v>144</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -4049,7 +4064,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="B29" s="11" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -4080,7 +4095,7 @@
         <v>154</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" cm="1" t="str">
@@ -4102,7 +4117,7 @@
         <v>159</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21" cm="1" t="str">
@@ -4124,7 +4139,7 @@
         <v>163</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>165</v>
@@ -4148,7 +4163,7 @@
         <v>168</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>259</v>
@@ -4271,7 +4286,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -4284,10 +4299,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4307,16 +4322,16 @@
         <v>13</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="M5" s="27" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4386,10 +4401,10 @@
         <v>80</v>
       </c>
       <c r="I8" s="27" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="J8" s="27" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="L8" s="5">
         <v>50</v>
@@ -4476,10 +4491,10 @@
         <v>60</v>
       </c>
       <c r="L12" s="27" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="M12" s="27" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -4502,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -4525,7 +4540,7 @@
         <v>60</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -4548,7 +4563,7 @@
         <v>70</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -4571,7 +4586,7 @@
         <v>80</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -4594,7 +4609,7 @@
         <v>90</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -4676,7 +4691,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4687,7 +4702,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -4706,7 +4721,7 @@
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -4717,19 +4732,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="7" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C6" s="31"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="7" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C7" s="31"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="7" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C8" s="32" cm="1" t="str">
         <f t="array" ref="C8">IF(OR(C6="",C7=""),"",ROUND(MOD(C7-C6,1)*1440,0))</f>
@@ -4738,7 +4753,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="7" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="C9" s="32">
         <v>15</v>
@@ -4746,7 +4761,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="7" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C10" s="12" cm="1" t="str">
         <f t="array" ref="C10">IF(AND(SUM('F4-1 Seeker'!$G$12:$G$34)&gt;=160*0.5,SUM('F4-2 Safety Net'!$G$12:$G$34)&gt;=160*0.5,SUM('F4-3 Old School'!$G$12:$G$34)&gt;=160*0.5,SUM('F4-4 Power Couple'!$G$14:$G$42)&gt;=220*0.5,SUM('F4-5 Tiers'!$G$12:$G$34)&gt;=160*0.5),"OPEN","LOCKED")</f>
@@ -4759,7 +4774,7 @@
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -4793,7 +4808,7 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="B14" s="33" cm="1" t="str">
         <f t="array" ref="B14">IF($C$10="OPEN","Which XLOOKUP match_mode returns an exact match or the next smaller item?  (from F4-5 Tiers)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4816,7 +4831,7 @@
     </row>
     <row r="15" spans="1:7" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B15" s="33" cm="1" t="str">
         <f t="array" ref="B15">IF($C$10="OPEN","For an approximate VLOOKUP, how must the first column be sorted?  (from F4-5 Tiers)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4839,7 +4854,7 @@
     </row>
     <row r="16" spans="1:7" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="B16" s="33" cm="1" t="str">
         <f t="array" ref="B16">IF($C$10="OPEN","Which XLOOKUP argument number sets the result when no match is found?  (from F4-2 Safety Net)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4862,7 +4877,7 @@
     </row>
     <row r="17" spans="1:7" ht="51.25" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B17" s="33" cm="1" t="str">
         <f t="array" ref="B17">IF($C$10="OPEN","If the return array is E6:F20, how many columns does the result spill into?  (from F4-2 Safety Net)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4885,7 +4900,7 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B18" s="33" cm="1" t="str">
         <f t="array" ref="B18">IF($C$10="OPEN","Which wildcard matches any number of characters?  (from F3-1 Counters)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4908,7 +4923,7 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="B19" s="33" cm="1" t="str">
         <f t="array" ref="B19">IF($C$10="OPEN","Which function adds values that meet one condition?  (from F3-2 Money Bags)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4931,7 +4946,7 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B20" s="33" cm="1" t="str">
         <f t="array" ref="B20">IF($C$10="OPEN","Which function averages values that meet one condition?  (from F3-2 Money Bags)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4954,7 +4969,7 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="B21" s="33" cm="1" t="str">
         <f t="array" ref="B21">IF($C$10="OPEN","Which function counts rows that meet several conditions?  (from F3-3 Multi-Filter)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4977,7 +4992,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -4988,7 +5003,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -5016,14 +5031,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="B26" s="33" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In J6 return the Price of the ID in I6 with XLOOKUP.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$6),ABS('Boss Arena'!$J$6-Key!$C$96)&lt;=1E-9*MAX(1,ABS(Key!$C$96))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use XLOOKUP"))))),"LOCKED")</f>
@@ -5041,17 +5056,17 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B27" s="33" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In J9 return the Stock of I9 with locked ranges, then fill down to J12.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
-        <f t="array" ref="D27">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$J$9,'Boss Arena'!$J$10,'Boss Arena'!$J$11,'Boss Arena'!$J$12)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$12))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$J$9),ISERROR('Boss Arena'!$J$10),ISERROR('Boss Arena'!$J$11),ISERROR('Boss Arena'!$J$12)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$9),ABS('Boss Arena'!$J$9-Key!$E$97)&lt;=1E-9*MAX(1,ABS(Key!$E$97))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$J$10),ABS('Boss Arena'!$J$10-Key!$F$97)&lt;=1E-9*MAX(1,ABS(Key!$F$97))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$J$11),ABS('Boss Arena'!$J$11-Key!$G$97)&lt;=1E-9*MAX(1,ABS(Key!$G$97))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$J$12),ABS('Boss Arena'!$J$12-Key!$H$97)&lt;=1E-9*MAX(1,ABS(Key!$H$97))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$9)))))),IF(ISNUMBER(FIND("$",_xlfn.FORMULATEXT('Boss Arena'!$J$9))),"✔ CLEAR","✘ CLOSE · add $ so it fills correctly (F4)"),"✘ CLOSE · right value, but use XLOOKUP"))))),"LOCKED")</f>
+        <f t="array" ref="D27">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$J$9,'Boss Arena'!$J$10,'Boss Arena'!$J$11,'Boss Arena'!$J$12)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$J$12))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$J$9),ISERROR('Boss Arena'!$J$10),ISERROR('Boss Arena'!$J$11),ISERROR('Boss Arena'!$J$12)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$9),ABS('Boss Arena'!$J$9-Key!$E$97)&lt;=1E-9*MAX(1,ABS(Key!$E$97))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$J$10),ABS('Boss Arena'!$J$10-Key!$F$97)&lt;=1E-9*MAX(1,ABS(Key!$F$97))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$J$11),ABS('Boss Arena'!$J$11-Key!$G$97)&lt;=1E-9*MAX(1,ABS(Key!$G$97))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$J$12),ABS('Boss Arena'!$J$12-Key!$H$97)&lt;=1E-9*MAX(1,ABS(Key!$H$97))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$9))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"VLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$9))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"INDEX"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$9))))))),IF(ISNUMBER(FIND("$",_xlfn.FORMULATEXT('Boss Arena'!$J$9))),"✔ CLEAR","✘ CLOSE · add $ so it fills correctly (F4)"),"✘ CLOSE · right value, but use XLOOKUP/VLOOKUP/INDEX"))))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E27" s="22"/>
@@ -5066,17 +5081,17 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="B28" s="33" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In J15 look up the Product for I15 and show ""Not found"" when it is missing.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
-        <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$15),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$15)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$15),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$15),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$J$15),'Boss Arena'!$J$15=Key!$C$98),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$15)))))),"✔ CLEAR","✘ CLOSE · right value, but use XLOOKUP"))))),"LOCKED")</f>
+        <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$15),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$15)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$15),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$15),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$J$15),'Boss Arena'!$J$15=Key!$C$98),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$15))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"VLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$15))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"INDEX"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$15))))))),"✔ CLEAR","✘ CLOSE · right value, but use XLOOKUP/VLOOKUP/INDEX"))))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E28" s="22"/>
@@ -5091,14 +5106,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="B29" s="33" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In J18 return the Price AND the Stock of I18 with one XLOOKUP.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$18),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$18)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$18),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$18),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$J$18))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2101)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$J$18))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2101)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$J$18)=_xlfn.ANCHORARRAY(Key!$E$2101)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2101))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2101))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$18)))))),"✔ CLEAR","✘ CLOSE · right result, but use XLOOKUP"),"✘ TRY AGAIN")))),"LOCKED")</f>
@@ -5116,14 +5131,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B30" s="33" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In J21 return the Category of I21 with VLOOKUP (exact match).","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$21),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$21)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$21),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$21),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$J$21),'Boss Arena'!$J$21=Key!$C$100),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"VLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$21)))))),"✔ CLEAR","✘ CLOSE · right value, but use VLOOKUP"))))),"LOCKED")</f>
@@ -5141,14 +5156,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B31" s="33" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In J24 return the ID of the product named in I24 (the ID is to the LEFT). Use INDEX and MATCH.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$24),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$24)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$24),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$24),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$J$24),'Boss Arena'!$J$24=Key!$C$101),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"INDEX"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$24))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MATCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$24)))))),"✔ CLEAR","✘ CLOSE · right value, but use INDEX and MATCH"))))),"LOCKED")</f>
@@ -5166,14 +5181,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="B32" s="33" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In J27 return the position of I27 in C6:C20 with XMATCH.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$27),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$27)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$27),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$27),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$27),ABS('Boss Arena'!$J$27-Key!$C$102)&lt;=1E-9*MAX(1,ABS(Key!$C$102))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XMATCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$27)))))),"✔ CLEAR","✘ CLOSE · right value, but use XMATCH"))))),"LOCKED")</f>
@@ -5191,17 +5206,17 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="B33" s="33" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","In J30 find the discount tier for the quantity in I30 from L6:M9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
-        <f t="array" ref="D33">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$30),ABS('Boss Arena'!$J$30-Key!$C$103)&lt;=1E-9*MAX(1,ABS(Key!$C$103))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$30)))))),IF(ISNUMBER(FIND("-1",_xlfn.FORMULATEXT('Boss Arena'!$J$30))),"✔ CLEAR","✘ CLOSE · your formula needs -1"),"✘ CLOSE · right value, but use XLOOKUP"))))),"LOCKED")</f>
+        <f t="array" ref="D33">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$30),ABS('Boss Arena'!$J$30-Key!$C$103)&lt;=1E-9*MAX(1,ABS(Key!$C$103))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$30))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"VLOOKUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$30))))))),"✔ CLEAR","✘ CLOSE · right value, but use XLOOKUP/VLOOKUP"))))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E33" s="22"/>
@@ -5316,7 +5331,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -5329,10 +5344,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -5358,10 +5373,10 @@
         <v>12</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="M5" s="27" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5590,7 +5605,7 @@
         <v>150</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="J15" s="28"/>
     </row>
@@ -5706,7 +5721,7 @@
     </row>
     <row r="23" spans="2:11">
       <c r="I23" s="27" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="J23" s="27" t="s">
         <v>9</v>
@@ -5720,10 +5735,10 @@
     </row>
     <row r="26" spans="2:11">
       <c r="I26" s="27" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="J26" s="27" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="27" spans="2:11">
@@ -5734,10 +5749,10 @@
     </row>
     <row r="29" spans="2:11">
       <c r="I29" s="27" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="30" spans="2:11">
@@ -5771,7 +5786,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5779,189 +5794,189 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="51.25" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>54</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>57</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>142</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="35.5" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>179</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="35.5" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>141</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="35.5" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>134</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="35.5" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>135</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="35.5" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>238</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="19.75" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>341</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>242</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>143</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
   </sheetData>
@@ -6882,13 +6897,28 @@
       <c r="F47" t="s">
         <v>355</v>
       </c>
+      <c r="G47" t="s">
+        <v>356</v>
+      </c>
+      <c r="H47" t="s">
+        <v>357</v>
+      </c>
+      <c r="I47" t="s">
+        <v>358</v>
+      </c>
+      <c r="J47" t="s">
+        <v>359</v>
+      </c>
+      <c r="K47" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="48" spans="1:20">
       <c r="A48" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B48" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C48" cm="1" t="str">
         <f t="array" ref="C48">VLOOKUP('F4-3 Arena'!$I$6,'F4-3 Arena'!$B$6:$F$20,3,FALSE)</f>
@@ -6897,10 +6927,10 @@
     </row>
     <row r="49" spans="1:20">
       <c r="A49" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B49" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C49" cm="1">
         <f t="array" ref="C49">VLOOKUP('F4-3 Arena'!$I$9,'F4-3 Arena'!$B$6:$F$20,5,FALSE)</f>
@@ -6909,7 +6939,7 @@
     </row>
     <row r="50" spans="1:20">
       <c r="A50" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B50" t="s">
         <v>340</v>
@@ -6935,7 +6965,7 @@
     </row>
     <row r="51" spans="1:20">
       <c r="A51" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B51" t="s">
         <v>344</v>
@@ -6946,173 +6976,188 @@
       <c r="F51" t="s">
         <v>355</v>
       </c>
+      <c r="G51" t="s">
+        <v>356</v>
+      </c>
+      <c r="H51" t="s">
+        <v>357</v>
+      </c>
+      <c r="I51" t="s">
+        <v>358</v>
+      </c>
+      <c r="J51" t="s">
+        <v>359</v>
+      </c>
+      <c r="K51" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="52" spans="1:20">
       <c r="A52" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B52" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E52" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F52" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="53" spans="1:20">
       <c r="A53" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B53" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="E53" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F53" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="54" spans="1:20">
       <c r="A54" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B54" t="s">
         <v>65</v>
       </c>
       <c r="E54" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="55" spans="1:20">
       <c r="A55" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B55" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="E55" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="56" spans="1:20">
       <c r="A56" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B56" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E56" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F56" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="G56" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="H56" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="57" spans="1:20">
       <c r="A57" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B57" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E57" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F57" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="G57" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="H57" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="58" spans="1:20">
       <c r="A58" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B58" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E58" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F58" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="59" spans="1:20">
       <c r="A59" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B59" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="E59" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="F59" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="G59" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="H59" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="I59" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="J59" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="K59" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="L59" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="M59" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="N59" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="O59" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="P59" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="Q59" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="R59" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="S59" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="T59" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="60" spans="1:20">
       <c r="A60" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B60" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C60" t="s">
         <v>134</v>
@@ -7132,10 +7177,10 @@
     </row>
     <row r="61" spans="1:20">
       <c r="A61" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B61" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C61" t="s">
         <v>135</v>
@@ -7155,10 +7200,10 @@
     </row>
     <row r="62" spans="1:20">
       <c r="A62" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B62" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C62" t="s">
         <v>238</v>
@@ -7178,10 +7223,10 @@
     </row>
     <row r="63" spans="1:20">
       <c r="A63" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B63" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C63" t="s">
         <v>341</v>
@@ -7201,99 +7246,132 @@
     </row>
     <row r="64" spans="1:20">
       <c r="A64" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B64" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="E64" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F64" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="G64" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="H64" t="s">
         <v>134</v>
       </c>
       <c r="I64" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="J64" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="65" spans="1:20">
       <c r="A65" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="E65" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F65" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="G65" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="H65" t="s">
         <v>135</v>
       </c>
       <c r="I65" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="J65" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="66" spans="1:20">
       <c r="A66" t="s">
+        <v>467</v>
+      </c>
+      <c r="B66" t="s">
+        <v>447</v>
+      </c>
+      <c r="E66" t="s">
         <v>462</v>
       </c>
-      <c r="B66" t="s">
-        <v>442</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
+        <v>463</v>
+      </c>
+      <c r="G66" t="s">
+        <v>464</v>
+      </c>
+      <c r="H66" t="s">
+        <v>468</v>
+      </c>
+      <c r="I66" t="s">
+        <v>469</v>
+      </c>
+      <c r="J66" t="s">
+        <v>470</v>
+      </c>
+      <c r="K66" t="s">
         <v>135</v>
+      </c>
+      <c r="L66" t="s">
+        <v>465</v>
+      </c>
+      <c r="M66" t="s">
+        <v>466</v>
+      </c>
+      <c r="N66" t="s">
+        <v>341</v>
+      </c>
+      <c r="O66" t="s">
+        <v>471</v>
+      </c>
+      <c r="P66" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="67" spans="1:20">
       <c r="A67" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="B67" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E67" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F67" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G67" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="H67" t="s">
         <v>341</v>
       </c>
       <c r="I67" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="J67" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="68" spans="1:20">
       <c r="A68" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B68" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C68" cm="1">
         <f t="array" ref="C68">MATCH('F4-4 Arena'!$I$6,'F4-4 Arena'!$C$6:$C$20,0)</f>
@@ -7302,10 +7380,10 @@
     </row>
     <row r="69" spans="1:20">
       <c r="A69" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B69" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C69" cm="1" t="str">
         <f t="array" ref="C69">INDEX('F4-4 Arena'!$B$6:$B$20,MATCH('F4-4 Arena'!$I$9,'F4-4 Arena'!$C$6:$C$20,0))</f>
@@ -7314,10 +7392,10 @@
     </row>
     <row r="70" spans="1:20">
       <c r="A70" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B70" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C70" cm="1">
         <f t="array" ref="C70">_xlfn.XMATCH('F4-4 Arena'!$I$12,'F4-4 Arena'!$C$6:$C$20)</f>
@@ -7326,10 +7404,10 @@
     </row>
     <row r="71" spans="1:20">
       <c r="A71" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B71" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C71" cm="1">
         <f t="array" ref="C71">INDEX('F4-4 Arena'!$E$6:$E$20,5)</f>
@@ -7338,96 +7416,129 @@
     </row>
     <row r="72" spans="1:20">
       <c r="A72" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B72" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="E72" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F72" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="G72" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="H72" t="s">
         <v>134</v>
       </c>
       <c r="I72" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="J72" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="73" spans="1:20">
       <c r="A73" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B73" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="E73" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F73" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="G73" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="H73" t="s">
         <v>135</v>
       </c>
       <c r="I73" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="J73" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="74" spans="1:20">
       <c r="A74" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B74" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="E74" t="s">
+        <v>462</v>
+      </c>
+      <c r="F74" t="s">
+        <v>463</v>
+      </c>
+      <c r="G74" t="s">
+        <v>464</v>
+      </c>
+      <c r="H74" t="s">
+        <v>468</v>
+      </c>
+      <c r="I74" t="s">
+        <v>469</v>
+      </c>
+      <c r="J74" t="s">
+        <v>470</v>
+      </c>
+      <c r="K74" t="s">
         <v>135</v>
+      </c>
+      <c r="L74" t="s">
+        <v>465</v>
+      </c>
+      <c r="M74" t="s">
+        <v>466</v>
+      </c>
+      <c r="N74" t="s">
+        <v>341</v>
+      </c>
+      <c r="O74" t="s">
+        <v>471</v>
+      </c>
+      <c r="P74" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="75" spans="1:20">
       <c r="A75" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B75" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E75" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F75" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G75" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="H75" t="s">
         <v>341</v>
       </c>
       <c r="I75" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="J75" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="76" spans="1:20">
       <c r="A76" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B76" t="s">
         <v>133</v>
@@ -7453,7 +7564,7 @@
     </row>
     <row r="77" spans="1:20">
       <c r="A77" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B77" t="s">
         <v>140</v>
@@ -7470,117 +7581,117 @@
     </row>
     <row r="78" spans="1:20">
       <c r="A78" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B78" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="E78" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="F78" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="G78" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="H78" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="I78" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="J78" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="K78" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="L78" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="M78" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="N78" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="O78" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="P78" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="Q78" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="R78" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="S78" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="T78" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
     </row>
     <row r="79" spans="1:20">
       <c r="A79" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B79" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="E79" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="F79" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="80" spans="1:20">
       <c r="A80" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B80" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="E80" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="F80" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="G80" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="H80" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="I80" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="J80" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="B81" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="E81" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B82" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C82" t="s">
         <v>242</v>
@@ -7600,10 +7711,10 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B83" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C83" t="s">
         <v>143</v>
@@ -7623,41 +7734,41 @@
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B84" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="E84" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="B85" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="E85" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="F85" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="G85" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="H85" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B86" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C86" cm="1">
         <f t="array" ref="C86">_xlfn.XLOOKUP('F4-5 Arena'!$I$6,'F4-5 Arena'!$L$6:$L$9,'F4-5 Arena'!$M$6:$M$9,,-1)</f>
@@ -7666,10 +7777,10 @@
     </row>
     <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B87" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C87" cm="1" t="str">
         <f t="array" ref="C87">VLOOKUP('F4-5 Arena'!$I$9,'F4-5 Arena'!$L$13:$M$17,2,TRUE)</f>
@@ -7678,38 +7789,38 @@
     </row>
     <row r="88" spans="1:10">
       <c r="A88" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B88" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="E88" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="B89" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="E89" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="F89" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="G89" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="H89" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="B90" t="s">
         <v>237</v>
@@ -7729,7 +7840,7 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B91" t="s">
         <v>241</v>
@@ -7743,102 +7854,102 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="B92" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="E92" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="F92" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="B93" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="E93" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="F93" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="G93" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="H93" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="I93" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="J93" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="B94" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="E94" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="F94" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="G94" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="H94" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="I94" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="J94" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B95" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="E95" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="F95" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="G95" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="H95" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="I95" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="J95" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="B96" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="C96" cm="1">
         <f t="array" ref="C96">_xlfn.XLOOKUP('Boss Arena'!$I$6,'Boss Arena'!$B$6:$B$20,'Boss Arena'!$E$6:$E$20)</f>
@@ -7847,10 +7958,10 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="B97" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="E97" cm="1">
         <f t="array" ref="E97">_xlfn.XLOOKUP('Boss Arena'!$I$9,'Boss Arena'!$B$6:$B$20,'Boss Arena'!$F$6:$F$20)</f>
@@ -7871,10 +7982,10 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B98" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="C98" cm="1" t="str">
         <f t="array" ref="C98">_xlfn.XLOOKUP('Boss Arena'!$I$15,'Boss Arena'!$B$6:$B$20,'Boss Arena'!$C$6:$C$20,"Not found")</f>
@@ -7883,18 +7994,18 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="B99" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="B100" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="C100" cm="1" t="str">
         <f t="array" ref="C100">VLOOKUP('Boss Arena'!$I$21,'Boss Arena'!$B$6:$F$20,3,FALSE)</f>
@@ -7903,10 +8014,10 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="B101" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="C101" cm="1" t="str">
         <f t="array" ref="C101">INDEX('Boss Arena'!$B$6:$B$20,MATCH('Boss Arena'!$I$24,'Boss Arena'!$C$6:$C$20,0))</f>
@@ -7915,10 +8026,10 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="B102" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="C102" cm="1">
         <f t="array" ref="C102">_xlfn.XMATCH('Boss Arena'!$I$27,'Boss Arena'!$C$6:$C$20)</f>
@@ -7927,10 +8038,10 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="B103" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="C103" cm="1">
         <f t="array" ref="C103">_xlfn.XLOOKUP('Boss Arena'!$I$30,'Boss Arena'!$L$6:$L$9,'Boss Arena'!$M$6:$M$9,,-1)</f>
@@ -9961,7 +10072,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9972,7 +10083,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -10439,11 +10550,11 @@
         <v>159</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21" cm="1" t="str">
-        <f t="array" ref="D32">IFERROR(_xlfn.LET(_xlpm.a,'F4-3 Old School'!$C$32,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$47:$F$47),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D32">IFERROR(_xlfn.LET(_xlpm.a,'F4-3 Old School'!$C$32,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$47:$K$47),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E32" s="22"/>
@@ -10461,7 +10572,7 @@
         <v>163</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>165</v>
@@ -10485,7 +10596,7 @@
         <v>168</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>259</v>
@@ -10947,7 +11058,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10958,7 +11069,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -11010,7 +11121,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>134</v>
@@ -11021,7 +11132,7 @@
         <v>55</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>135</v>
@@ -11029,10 +11140,10 @@
     </row>
     <row r="9" spans="1:7" ht="67" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>238</v>
@@ -11043,7 +11154,7 @@
         <v>246</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>341</v>
@@ -11088,7 +11199,7 @@
         <v>67</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -11110,11 +11221,11 @@
         <v>72</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
-        <f t="array" ref="D15">IFERROR(_xlfn.LET(_xlpm.a,'F4-4 Power Couple'!$C$15,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$51:$F$51),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D15">IFERROR(_xlfn.LET(_xlpm.a,'F4-4 Power Couple'!$C$15,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$51:$K$51),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E15" s="22"/>
@@ -11132,7 +11243,7 @@
         <v>79</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -11154,7 +11265,7 @@
         <v>99</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -11176,7 +11287,7 @@
         <v>104</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -11198,7 +11309,7 @@
         <v>109</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -11220,7 +11331,7 @@
         <v>114</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -11242,7 +11353,7 @@
         <v>119</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -11264,7 +11375,7 @@
         <v>124</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -11286,7 +11397,7 @@
         <v>129</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" cm="1" t="str">
@@ -11342,7 +11453,7 @@
         <v>137</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -11364,7 +11475,7 @@
         <v>144</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -11383,10 +11494,10 @@
     </row>
     <row r="29" spans="1:7" ht="51.25" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="21" cm="1" t="str">
@@ -11405,10 +11516,10 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="21" cm="1" t="str">
@@ -11438,7 +11549,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="11" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -11469,7 +11580,7 @@
         <v>154</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -11491,7 +11602,7 @@
         <v>159</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="21" cm="1" t="str">
@@ -11513,11 +11624,11 @@
         <v>163</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="21" cm="1" t="str">
-        <f t="array" ref="D37">IFERROR(_xlfn.LET(_xlpm.a,'F4-4 Power Couple'!$C$37,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$66:$E$66),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D37">IFERROR(_xlfn.LET(_xlpm.a,'F4-4 Power Couple'!$C$37,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$66:$P$66),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E37" s="22"/>
@@ -11535,7 +11646,7 @@
         <v>168</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -11554,13 +11665,13 @@
     </row>
     <row r="39" spans="1:7" ht="35.5" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(ISBLANK('F4-4 Arena'!$J$6),"",IF(NOT(_xlfn.ISFORMULA('F4-4 Arena'!$J$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F4-4 Arena'!$J$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F4-4 Arena'!$J$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F4-4 Arena'!$J$6),ABS('F4-4 Arena'!$J$6-Key!$C$68)&lt;=1E-9*MAX(1,ABS(Key!$C$68))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MATCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-4 Arena'!$J$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use MATCH")))))</f>
@@ -11578,13 +11689,13 @@
     </row>
     <row r="40" spans="1:7" ht="51.25" customHeight="1">
       <c r="A40" s="18" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D40" s="21" cm="1" t="str">
         <f t="array" ref="D40">IF(ISBLANK('F4-4 Arena'!$J$9),"",IF(NOT(_xlfn.ISFORMULA('F4-4 Arena'!$J$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F4-4 Arena'!$J$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F4-4 Arena'!$J$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F4-4 Arena'!$J$9),'F4-4 Arena'!$J$9=Key!$C$69),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"INDEX"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-4 Arena'!$J$9))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MATCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-4 Arena'!$J$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use INDEX and MATCH")))))</f>
@@ -11602,13 +11713,13 @@
     </row>
     <row r="41" spans="1:7" ht="35.5" customHeight="1">
       <c r="A41" s="18" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="D41" s="21" cm="1" t="str">
         <f t="array" ref="D41">IF(ISBLANK('F4-4 Arena'!$J$12),"",IF(NOT(_xlfn.ISFORMULA('F4-4 Arena'!$J$12)),"✘ That's a typed value · enter a formula",IF(ISERROR('F4-4 Arena'!$J$12),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F4-4 Arena'!$J$12),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F4-4 Arena'!$J$12),ABS('F4-4 Arena'!$J$12-Key!$C$70)&lt;=1E-9*MAX(1,ABS(Key!$C$70))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"XMATCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-4 Arena'!$J$12)))))),"✔ CLEAR","✘ CLOSE · right value, but use XMATCH")))))</f>
@@ -11626,13 +11737,13 @@
     </row>
     <row r="42" spans="1:7" ht="35.5" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D42" s="21" cm="1" t="str">
         <f t="array" ref="D42">IF(ISBLANK('F4-4 Arena'!$J$14),"",IF(NOT(_xlfn.ISFORMULA('F4-4 Arena'!$J$14)),"✘ That's a typed value · enter a formula",IF(ISERROR('F4-4 Arena'!$J$14),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F4-4 Arena'!$J$14),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F4-4 Arena'!$J$14),ABS('F4-4 Arena'!$J$14-Key!$C$71)&lt;=1E-9*MAX(1,ABS(Key!$C$71))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"INDEX"&amp;"(",UPPER(_xlfn.FORMULATEXT('F4-4 Arena'!$J$14)))))),"✔ CLEAR","✘ CLOSE · right value, but use INDEX")))))</f>
@@ -11780,7 +11891,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -11793,10 +11904,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -11816,10 +11927,10 @@
         <v>13</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -11877,7 +11988,7 @@
         <v>80</v>
       </c>
       <c r="I8" s="27" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="J8" s="27" t="s">
         <v>9</v>
@@ -11938,7 +12049,7 @@
         <v>25</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="J11" s="27" t="s">
         <v>341</v>
@@ -11999,7 +12110,7 @@
         <v>40</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="J14" s="28"/>
     </row>
